--- a/Knowledge/Model Schema/PG/Model Output/PG_model_balance_test.xlsx
+++ b/Knowledge/Model Schema/PG/Model Output/PG_model_balance_test.xlsx
@@ -94,7 +94,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,7 +109,6 @@
     <xf numFmtId="166" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2495,75 +2494,75 @@
         <f>'YTD CF'!O13-'YTD CF'!N13</f>
         <v/>
       </c>
-      <c r="T13" s="12">
+      <c r="T13" s="7">
         <f>SUM(T2:T12)</f>
         <v/>
       </c>
-      <c r="U13" s="12">
+      <c r="U13" s="7">
         <f>SUM(U2:U12)</f>
         <v/>
       </c>
-      <c r="V13" s="12">
+      <c r="V13" s="7">
         <f>SUM(V2:V12)</f>
         <v/>
       </c>
-      <c r="W13" s="12">
+      <c r="W13" s="7">
         <f>SUM(W2:W12)</f>
         <v/>
       </c>
-      <c r="X13" s="12">
+      <c r="X13" s="7">
         <f>SUM(X2:X12)</f>
         <v/>
       </c>
-      <c r="Y13" s="12">
+      <c r="Y13" s="7">
         <f>SUM(Y2:Y12)</f>
         <v/>
       </c>
-      <c r="Z13" s="12">
+      <c r="Z13" s="7">
         <f>SUM(Z2:Z12)</f>
         <v/>
       </c>
-      <c r="AA13" s="12">
+      <c r="AA13" s="7">
         <f>SUM(AA2:AA12)</f>
         <v/>
       </c>
-      <c r="AB13" s="12">
+      <c r="AB13" s="7">
         <f>SUM(AB2:AB12)</f>
         <v/>
       </c>
-      <c r="AC13" s="12">
+      <c r="AC13" s="7">
         <f>SUM(AC2:AC12)</f>
         <v/>
       </c>
-      <c r="AD13" s="12">
+      <c r="AD13" s="7">
         <f>SUM(AD2:AD12)</f>
         <v/>
       </c>
-      <c r="AE13" s="12">
+      <c r="AE13" s="7">
         <f>SUM(AE2:AE12)</f>
         <v/>
       </c>
-      <c r="AF13" s="12">
+      <c r="AF13" s="7">
         <f>SUM(AF2:AF12)</f>
         <v/>
       </c>
-      <c r="AG13" s="12">
+      <c r="AG13" s="7">
         <f>SUM(AG2:AG12)</f>
         <v/>
       </c>
-      <c r="AH13" s="12">
+      <c r="AH13" s="7">
         <f>SUM(AH2:AH12)</f>
         <v/>
       </c>
-      <c r="AI13" s="12">
+      <c r="AI13" s="7">
         <f>SUM(AI2:AI12)</f>
         <v/>
       </c>
-      <c r="AJ13" s="12">
+      <c r="AJ13" s="7">
         <f>SUM(AJ2:AJ12)</f>
         <v/>
       </c>
-      <c r="AK13" s="12">
+      <c r="AK13" s="7">
         <f>SUM(AK2:AK12)</f>
         <v/>
       </c>
@@ -3385,75 +3384,75 @@
         <f>'YTD CF'!O19-'YTD CF'!N19</f>
         <v/>
       </c>
-      <c r="T19" s="12">
+      <c r="T19" s="7">
         <f>SUM(T14:T18)</f>
         <v/>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="7">
         <f>SUM(U14:U18)</f>
         <v/>
       </c>
-      <c r="V19" s="12">
+      <c r="V19" s="7">
         <f>SUM(V14:V18)</f>
         <v/>
       </c>
-      <c r="W19" s="12">
+      <c r="W19" s="7">
         <f>SUM(W14:W18)</f>
         <v/>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="7">
         <f>SUM(X14:X18)</f>
         <v/>
       </c>
-      <c r="Y19" s="12">
+      <c r="Y19" s="7">
         <f>SUM(Y14:Y18)</f>
         <v/>
       </c>
-      <c r="Z19" s="12">
+      <c r="Z19" s="7">
         <f>SUM(Z14:Z18)</f>
         <v/>
       </c>
-      <c r="AA19" s="12">
+      <c r="AA19" s="7">
         <f>SUM(AA14:AA18)</f>
         <v/>
       </c>
-      <c r="AB19" s="12">
+      <c r="AB19" s="7">
         <f>SUM(AB14:AB18)</f>
         <v/>
       </c>
-      <c r="AC19" s="12">
+      <c r="AC19" s="7">
         <f>SUM(AC14:AC18)</f>
         <v/>
       </c>
-      <c r="AD19" s="12">
+      <c r="AD19" s="7">
         <f>SUM(AD14:AD18)</f>
         <v/>
       </c>
-      <c r="AE19" s="12">
+      <c r="AE19" s="7">
         <f>SUM(AE14:AE18)</f>
         <v/>
       </c>
-      <c r="AF19" s="12">
+      <c r="AF19" s="7">
         <f>SUM(AF14:AF18)</f>
         <v/>
       </c>
-      <c r="AG19" s="12">
+      <c r="AG19" s="7">
         <f>SUM(AG14:AG18)</f>
         <v/>
       </c>
-      <c r="AH19" s="12">
+      <c r="AH19" s="7">
         <f>SUM(AH14:AH18)</f>
         <v/>
       </c>
-      <c r="AI19" s="12">
+      <c r="AI19" s="7">
         <f>SUM(AI14:AI18)</f>
         <v/>
       </c>
-      <c r="AJ19" s="12">
+      <c r="AJ19" s="7">
         <f>SUM(AJ14:AJ18)</f>
         <v/>
       </c>
-      <c r="AK19" s="12">
+      <c r="AK19" s="7">
         <f>SUM(AK14:AK18)</f>
         <v/>
       </c>
@@ -4744,75 +4743,75 @@
         <f>'YTD CF'!O28-'YTD CF'!N28</f>
         <v/>
       </c>
-      <c r="T28" s="12">
+      <c r="T28" s="7">
         <f>SUM(T20:T27)</f>
         <v/>
       </c>
-      <c r="U28" s="12">
+      <c r="U28" s="7">
         <f>SUM(U20:U27)</f>
         <v/>
       </c>
-      <c r="V28" s="12">
+      <c r="V28" s="7">
         <f>SUM(V20:V27)</f>
         <v/>
       </c>
-      <c r="W28" s="12">
+      <c r="W28" s="7">
         <f>SUM(W20:W27)</f>
         <v/>
       </c>
-      <c r="X28" s="12">
+      <c r="X28" s="7">
         <f>SUM(X20:X27)</f>
         <v/>
       </c>
-      <c r="Y28" s="12">
+      <c r="Y28" s="7">
         <f>SUM(Y20:Y27)</f>
         <v/>
       </c>
-      <c r="Z28" s="12">
+      <c r="Z28" s="7">
         <f>SUM(Z20:Z27)</f>
         <v/>
       </c>
-      <c r="AA28" s="12">
+      <c r="AA28" s="7">
         <f>SUM(AA20:AA27)</f>
         <v/>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="7">
         <f>SUM(AB20:AB27)</f>
         <v/>
       </c>
-      <c r="AC28" s="12">
+      <c r="AC28" s="7">
         <f>SUM(AC20:AC27)</f>
         <v/>
       </c>
-      <c r="AD28" s="12">
+      <c r="AD28" s="7">
         <f>SUM(AD20:AD27)</f>
         <v/>
       </c>
-      <c r="AE28" s="12">
+      <c r="AE28" s="7">
         <f>SUM(AE20:AE27)</f>
         <v/>
       </c>
-      <c r="AF28" s="12">
+      <c r="AF28" s="7">
         <f>SUM(AF20:AF27)</f>
         <v/>
       </c>
-      <c r="AG28" s="12">
+      <c r="AG28" s="7">
         <f>SUM(AG20:AG27)</f>
         <v/>
       </c>
-      <c r="AH28" s="12">
+      <c r="AH28" s="7">
         <f>SUM(AH20:AH27)</f>
         <v/>
       </c>
-      <c r="AI28" s="12">
+      <c r="AI28" s="7">
         <f>SUM(AI20:AI27)</f>
         <v/>
       </c>
-      <c r="AJ28" s="12">
+      <c r="AJ28" s="7">
         <f>SUM(AJ20:AJ27)</f>
         <v/>
       </c>
-      <c r="AK28" s="12">
+      <c r="AK28" s="7">
         <f>SUM(AK20:AK27)</f>
         <v/>
       </c>
@@ -5046,75 +5045,75 @@
         <f>'YTD CF'!O30-'YTD CF'!N30</f>
         <v/>
       </c>
-      <c r="T30" s="12">
+      <c r="T30" s="7">
         <f>T13+T19+T28+T29</f>
         <v/>
       </c>
-      <c r="U30" s="12">
+      <c r="U30" s="7">
         <f>U13+U19+U28+U29</f>
         <v/>
       </c>
-      <c r="V30" s="12">
+      <c r="V30" s="7">
         <f>V13+V19+V28+V29</f>
         <v/>
       </c>
-      <c r="W30" s="12">
+      <c r="W30" s="7">
         <f>W13+W19+W28+W29</f>
         <v/>
       </c>
-      <c r="X30" s="12">
+      <c r="X30" s="7">
         <f>X13+X19+X28+X29</f>
         <v/>
       </c>
-      <c r="Y30" s="12">
+      <c r="Y30" s="7">
         <f>Y13+Y19+Y28+Y29</f>
         <v/>
       </c>
-      <c r="Z30" s="12">
+      <c r="Z30" s="7">
         <f>Z13+Z19+Z28+Z29</f>
         <v/>
       </c>
-      <c r="AA30" s="12">
+      <c r="AA30" s="7">
         <f>AA13+AA19+AA28+AA29</f>
         <v/>
       </c>
-      <c r="AB30" s="12">
+      <c r="AB30" s="7">
         <f>AB13+AB19+AB28+AB29</f>
         <v/>
       </c>
-      <c r="AC30" s="12">
+      <c r="AC30" s="7">
         <f>AC13+AC19+AC28+AC29</f>
         <v/>
       </c>
-      <c r="AD30" s="12">
+      <c r="AD30" s="7">
         <f>AD13+AD19+AD28+AD29</f>
         <v/>
       </c>
-      <c r="AE30" s="12">
+      <c r="AE30" s="7">
         <f>AE13+AE19+AE28+AE29</f>
         <v/>
       </c>
-      <c r="AF30" s="12">
+      <c r="AF30" s="7">
         <f>AF13+AF19+AF28+AF29</f>
         <v/>
       </c>
-      <c r="AG30" s="12">
+      <c r="AG30" s="7">
         <f>AG13+AG19+AG28+AG29</f>
         <v/>
       </c>
-      <c r="AH30" s="12">
+      <c r="AH30" s="7">
         <f>AH13+AH19+AH28+AH29</f>
         <v/>
       </c>
-      <c r="AI30" s="12">
+      <c r="AI30" s="7">
         <f>AI13+AI19+AI28+AI29</f>
         <v/>
       </c>
-      <c r="AJ30" s="12">
+      <c r="AJ30" s="7">
         <f>AJ13+AJ19+AJ28+AJ29</f>
         <v/>
       </c>
-      <c r="AK30" s="12">
+      <c r="AK30" s="7">
         <f>AK13+AK19+AK28+AK29</f>
         <v/>
       </c>
@@ -5365,131 +5364,131 @@
           <t>Net Sales / Revenue — Growth %</t>
         </is>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <f>IFERROR('QTR P&amp;L'!F2/'QTR P&amp;L'!B2-1,"")</f>
         <v/>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="12">
         <f>IFERROR('QTR P&amp;L'!G2/'QTR P&amp;L'!C2-1,"")</f>
         <v/>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="12">
         <f>IFERROR('QTR P&amp;L'!H2/'QTR P&amp;L'!D2-1,"")</f>
         <v/>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="12">
         <f>IFERROR('QTR P&amp;L'!I2/'QTR P&amp;L'!E2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="12">
         <f>IFERROR('QTR P&amp;L'!J2/'QTR P&amp;L'!F2-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="13">
+      <c r="K2" s="12">
         <f>IFERROR('QTR P&amp;L'!K2/'QTR P&amp;L'!G2-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="12">
         <f>IFERROR('QTR P&amp;L'!L2/'QTR P&amp;L'!H2-1,"")</f>
         <v/>
       </c>
-      <c r="M2" s="13">
+      <c r="M2" s="12">
         <f>IFERROR('QTR P&amp;L'!M2/'QTR P&amp;L'!I2-1,"")</f>
         <v/>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="12">
         <f>IFERROR('QTR P&amp;L'!N2/'QTR P&amp;L'!J2-1,"")</f>
         <v/>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="12">
         <f>IFERROR('QTR P&amp;L'!O2/'QTR P&amp;L'!K2-1,"")</f>
         <v/>
       </c>
-      <c r="P2" s="13">
+      <c r="P2" s="12">
         <f>IFERROR('QTR P&amp;L'!P2/'QTR P&amp;L'!L2-1,"")</f>
         <v/>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="12">
         <f>IFERROR('QTR P&amp;L'!Q2/'QTR P&amp;L'!M2-1,"")</f>
         <v/>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="12">
         <f>IFERROR('QTR P&amp;L'!R2/'QTR P&amp;L'!N2-1,"")</f>
         <v/>
       </c>
-      <c r="S2" s="13">
+      <c r="S2" s="12">
         <f>IFERROR('QTR P&amp;L'!S2/'QTR P&amp;L'!O2-1,"")</f>
         <v/>
       </c>
-      <c r="T2" s="14">
+      <c r="T2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="U2" s="14">
+      <c r="U2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="V2" s="14">
+      <c r="V2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="W2" s="14">
+      <c r="W2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="X2" s="14">
+      <c r="X2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="Y2" s="14">
+      <c r="Y2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="Z2" s="14">
+      <c r="Z2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AA2" s="14">
+      <c r="AA2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AB2" s="14">
+      <c r="AB2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AC2" s="14">
+      <c r="AC2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AD2" s="14">
+      <c r="AD2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AE2" s="14">
+      <c r="AE2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AF2" s="14">
+      <c r="AF2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AG2" s="14">
+      <c r="AG2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AH2" s="14">
+      <c r="AH2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AI2" s="14">
+      <c r="AI2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AJ2" s="14">
+      <c r="AJ2" s="13">
         <f>S2</f>
         <v/>
       </c>
-      <c r="AK2" s="14">
+      <c r="AK2" s="13">
         <f>S2</f>
         <v/>
       </c>
@@ -5500,147 +5499,147 @@
           <t>COGS — % of Revenue</t>
         </is>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <f>IFERROR('QTR P&amp;L'!B3/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <f>IFERROR('QTR P&amp;L'!C3/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <f>IFERROR('QTR P&amp;L'!D3/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <f>IFERROR('QTR P&amp;L'!E3/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <f>IFERROR('QTR P&amp;L'!F3/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <f>IFERROR('QTR P&amp;L'!G3/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <f>IFERROR('QTR P&amp;L'!H3/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <f>IFERROR('QTR P&amp;L'!I3/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <f>IFERROR('QTR P&amp;L'!J3/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <f>IFERROR('QTR P&amp;L'!K3/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <f>IFERROR('QTR P&amp;L'!L3/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <f>IFERROR('QTR P&amp;L'!M3/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="12">
         <f>IFERROR('QTR P&amp;L'!N3/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="12">
         <f>IFERROR('QTR P&amp;L'!O3/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="12">
         <f>IFERROR('QTR P&amp;L'!P3/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="12">
         <f>IFERROR('QTR P&amp;L'!Q3/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="12">
         <f>IFERROR('QTR P&amp;L'!R3/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S3" s="13">
+      <c r="S3" s="12">
         <f>IFERROR('QTR P&amp;L'!S3/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="W3" s="14">
+      <c r="W3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="X3" s="14">
+      <c r="X3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AC3" s="14">
+      <c r="AC3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AE3" s="14">
+      <c r="AE3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AG3" s="14">
+      <c r="AG3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AH3" s="14">
+      <c r="AH3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AI3" s="14">
+      <c r="AI3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AJ3" s="14">
+      <c r="AJ3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AK3" s="14">
+      <c r="AK3" s="13">
         <f>S3</f>
         <v/>
       </c>
@@ -5651,147 +5650,147 @@
           <t>SG&amp;A — % of Revenue</t>
         </is>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <f>IFERROR('QTR P&amp;L'!B5/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <f>IFERROR('QTR P&amp;L'!C5/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <f>IFERROR('QTR P&amp;L'!D5/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f>IFERROR('QTR P&amp;L'!E5/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <f>IFERROR('QTR P&amp;L'!F5/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <f>IFERROR('QTR P&amp;L'!G5/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f>IFERROR('QTR P&amp;L'!H5/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>IFERROR('QTR P&amp;L'!I5/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <f>IFERROR('QTR P&amp;L'!J5/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <f>IFERROR('QTR P&amp;L'!K5/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <f>IFERROR('QTR P&amp;L'!L5/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <f>IFERROR('QTR P&amp;L'!M5/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <f>IFERROR('QTR P&amp;L'!N5/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <f>IFERROR('QTR P&amp;L'!O5/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="12">
         <f>IFERROR('QTR P&amp;L'!P5/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="12">
         <f>IFERROR('QTR P&amp;L'!Q5/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="12">
         <f>IFERROR('QTR P&amp;L'!R5/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="12">
         <f>IFERROR('QTR P&amp;L'!S5/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AC4" s="14">
+      <c r="AC4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AF4" s="14">
+      <c r="AF4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AG4" s="14">
+      <c r="AG4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AH4" s="14">
+      <c r="AH4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AI4" s="14">
+      <c r="AI4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AJ4" s="14">
+      <c r="AJ4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AK4" s="14">
+      <c r="AK4" s="13">
         <f>S4</f>
         <v/>
       </c>
@@ -5802,147 +5801,147 @@
           <t>Impairment of Intangibles — % of Revenue</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <f>IFERROR('QTR P&amp;L'!B6/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>IFERROR('QTR P&amp;L'!C6/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>IFERROR('QTR P&amp;L'!D6/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>IFERROR('QTR P&amp;L'!E6/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>IFERROR('QTR P&amp;L'!F6/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>IFERROR('QTR P&amp;L'!G6/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>IFERROR('QTR P&amp;L'!H6/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>IFERROR('QTR P&amp;L'!I6/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>IFERROR('QTR P&amp;L'!J6/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <f>IFERROR('QTR P&amp;L'!K6/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <f>IFERROR('QTR P&amp;L'!L6/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>IFERROR('QTR P&amp;L'!M6/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f>IFERROR('QTR P&amp;L'!N6/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="12">
         <f>IFERROR('QTR P&amp;L'!O6/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <f>IFERROR('QTR P&amp;L'!P6/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="12">
         <f>IFERROR('QTR P&amp;L'!Q6/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="12">
         <f>IFERROR('QTR P&amp;L'!R6/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="12">
         <f>IFERROR('QTR P&amp;L'!S6/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="U5" s="14">
+      <c r="U5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="V5" s="14">
+      <c r="V5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="W5" s="14">
+      <c r="W5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="X5" s="14">
+      <c r="X5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="Y5" s="14">
+      <c r="Y5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="Z5" s="14">
+      <c r="Z5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AA5" s="14">
+      <c r="AA5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AB5" s="14">
+      <c r="AB5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AC5" s="14">
+      <c r="AC5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AD5" s="14">
+      <c r="AD5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AE5" s="14">
+      <c r="AE5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AF5" s="14">
+      <c r="AF5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AG5" s="14">
+      <c r="AG5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AH5" s="14">
+      <c r="AH5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AI5" s="14">
+      <c r="AI5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AJ5" s="14">
+      <c r="AJ5" s="13">
         <f>S5</f>
         <v/>
       </c>
-      <c r="AK5" s="14">
+      <c r="AK5" s="13">
         <f>S5</f>
         <v/>
       </c>
@@ -6025,75 +6024,75 @@
         <f>'QTR P&amp;L'!S8</f>
         <v/>
       </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="U6" s="15">
+      <c r="U6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="V6" s="15">
+      <c r="V6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="W6" s="15">
+      <c r="W6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="X6" s="15">
+      <c r="X6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="Y6" s="15">
+      <c r="Y6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="Z6" s="15">
+      <c r="Z6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AA6" s="15">
+      <c r="AA6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AB6" s="15">
+      <c r="AB6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AC6" s="15">
+      <c r="AC6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AD6" s="15">
+      <c r="AD6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AE6" s="15">
+      <c r="AE6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AF6" s="15">
+      <c r="AF6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AG6" s="15">
+      <c r="AG6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AH6" s="15">
+      <c r="AH6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AI6" s="15">
+      <c r="AI6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AJ6" s="15">
+      <c r="AJ6" s="14">
         <f>S6</f>
         <v/>
       </c>
-      <c r="AK6" s="15">
+      <c r="AK6" s="14">
         <f>S6</f>
         <v/>
       </c>
@@ -6176,75 +6175,75 @@
         <f>'QTR P&amp;L'!S9</f>
         <v/>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="U7" s="15">
+      <c r="U7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="V7" s="15">
+      <c r="V7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="W7" s="15">
+      <c r="W7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="X7" s="15">
+      <c r="X7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="Y7" s="15">
+      <c r="Y7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="Z7" s="15">
+      <c r="Z7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AA7" s="15">
+      <c r="AA7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AB7" s="15">
+      <c r="AB7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AC7" s="15">
+      <c r="AC7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AD7" s="15">
+      <c r="AD7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AE7" s="15">
+      <c r="AE7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AF7" s="15">
+      <c r="AF7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AG7" s="15">
+      <c r="AG7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AH7" s="15">
+      <c r="AH7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AI7" s="15">
+      <c r="AI7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AJ7" s="15">
+      <c r="AJ7" s="14">
         <f>S7</f>
         <v/>
       </c>
-      <c r="AK7" s="15">
+      <c r="AK7" s="14">
         <f>S7</f>
         <v/>
       </c>
@@ -6255,147 +6254,147 @@
           <t>Income Tax (Expense) Benefit — Effective Tax Rate %</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="12">
         <f>IFERROR('QTR P&amp;L'!B11/'QTR P&amp;L'!B10,"")</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="12">
         <f>IFERROR('QTR P&amp;L'!C11/'QTR P&amp;L'!C10,"")</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="12">
         <f>IFERROR('QTR P&amp;L'!D11/'QTR P&amp;L'!D10,"")</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="12">
         <f>IFERROR('QTR P&amp;L'!E11/'QTR P&amp;L'!E10,"")</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <f>IFERROR('QTR P&amp;L'!F11/'QTR P&amp;L'!F10,"")</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="12">
         <f>IFERROR('QTR P&amp;L'!G11/'QTR P&amp;L'!G10,"")</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f>IFERROR('QTR P&amp;L'!H11/'QTR P&amp;L'!H10,"")</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="12">
         <f>IFERROR('QTR P&amp;L'!I11/'QTR P&amp;L'!I10,"")</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="12">
         <f>IFERROR('QTR P&amp;L'!J11/'QTR P&amp;L'!J10,"")</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="12">
         <f>IFERROR('QTR P&amp;L'!K11/'QTR P&amp;L'!K10,"")</f>
         <v/>
       </c>
-      <c r="L8" s="13">
+      <c r="L8" s="12">
         <f>IFERROR('QTR P&amp;L'!L11/'QTR P&amp;L'!L10,"")</f>
         <v/>
       </c>
-      <c r="M8" s="13">
+      <c r="M8" s="12">
         <f>IFERROR('QTR P&amp;L'!M11/'QTR P&amp;L'!M10,"")</f>
         <v/>
       </c>
-      <c r="N8" s="13">
+      <c r="N8" s="12">
         <f>IFERROR('QTR P&amp;L'!N11/'QTR P&amp;L'!N10,"")</f>
         <v/>
       </c>
-      <c r="O8" s="13">
+      <c r="O8" s="12">
         <f>IFERROR('QTR P&amp;L'!O11/'QTR P&amp;L'!O10,"")</f>
         <v/>
       </c>
-      <c r="P8" s="13">
+      <c r="P8" s="12">
         <f>IFERROR('QTR P&amp;L'!P11/'QTR P&amp;L'!P10,"")</f>
         <v/>
       </c>
-      <c r="Q8" s="13">
+      <c r="Q8" s="12">
         <f>IFERROR('QTR P&amp;L'!Q11/'QTR P&amp;L'!Q10,"")</f>
         <v/>
       </c>
-      <c r="R8" s="13">
+      <c r="R8" s="12">
         <f>IFERROR('QTR P&amp;L'!R11/'QTR P&amp;L'!R10,"")</f>
         <v/>
       </c>
-      <c r="S8" s="13">
+      <c r="S8" s="12">
         <f>IFERROR('QTR P&amp;L'!S11/'QTR P&amp;L'!S10,"")</f>
         <v/>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="U8" s="14">
+      <c r="U8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="V8" s="14">
+      <c r="V8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="W8" s="14">
+      <c r="W8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="Z8" s="14">
+      <c r="Z8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AA8" s="14">
+      <c r="AA8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AB8" s="14">
+      <c r="AB8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AC8" s="14">
+      <c r="AC8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AD8" s="14">
+      <c r="AD8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AE8" s="14">
+      <c r="AE8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AF8" s="14">
+      <c r="AF8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AG8" s="14">
+      <c r="AG8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AH8" s="14">
+      <c r="AH8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AI8" s="14">
+      <c r="AI8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AJ8" s="14">
+      <c r="AJ8" s="13">
         <f>S8</f>
         <v/>
       </c>
-      <c r="AK8" s="14">
+      <c r="AK8" s="13">
         <f>S8</f>
         <v/>
       </c>
@@ -6478,75 +6477,75 @@
         <f>'QTR P&amp;L'!S13</f>
         <v/>
       </c>
-      <c r="T9" s="15">
+      <c r="T9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="U9" s="15">
+      <c r="U9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="V9" s="15">
+      <c r="V9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="W9" s="15">
+      <c r="W9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="X9" s="15">
+      <c r="X9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="Y9" s="15">
+      <c r="Y9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="Z9" s="15">
+      <c r="Z9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AA9" s="15">
+      <c r="AA9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AB9" s="15">
+      <c r="AB9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AC9" s="15">
+      <c r="AC9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AD9" s="15">
+      <c r="AD9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AE9" s="15">
+      <c r="AE9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AF9" s="15">
+      <c r="AF9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AG9" s="15">
+      <c r="AG9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AH9" s="15">
+      <c r="AH9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AI9" s="15">
+      <c r="AI9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AJ9" s="15">
+      <c r="AJ9" s="14">
         <f>S9</f>
         <v/>
       </c>
-      <c r="AK9" s="15">
+      <c r="AK9" s="14">
         <f>S9</f>
         <v/>
       </c>
@@ -6918,135 +6917,135 @@
           <t>Accounts Receivable — DSO (days)</t>
         </is>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="15">
         <f>IFERROR('QTR BS'!B3/'QTR P&amp;L'!B2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="C3" s="16">
+      <c r="C3" s="15">
         <f>IFERROR('QTR BS'!C3/'QTR P&amp;L'!C2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="D3" s="16">
+      <c r="D3" s="15">
         <f>IFERROR('QTR BS'!D3/'QTR P&amp;L'!D2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="E3" s="16">
+      <c r="E3" s="15">
         <f>IFERROR('QTR BS'!E3/'QTR P&amp;L'!E2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="15">
         <f>IFERROR('QTR BS'!F3/'QTR P&amp;L'!F2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="15">
         <f>IFERROR('QTR BS'!G3/'QTR P&amp;L'!G2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="15">
         <f>IFERROR('QTR BS'!H3/'QTR P&amp;L'!H2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="15">
         <f>IFERROR('QTR BS'!I3/'QTR P&amp;L'!I2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="15">
         <f>IFERROR('QTR BS'!J3/'QTR P&amp;L'!J2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="15">
         <f>IFERROR('QTR BS'!K3/'QTR P&amp;L'!K2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="15">
         <f>IFERROR('QTR BS'!L3/'QTR P&amp;L'!L2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="15">
         <f>IFERROR('QTR BS'!M3/'QTR P&amp;L'!M2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="15">
         <f>IFERROR('QTR BS'!N3/'QTR P&amp;L'!N2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="15">
         <f>IFERROR('QTR BS'!O3/'QTR P&amp;L'!O2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="15">
         <f>IFERROR('QTR BS'!P3/'QTR P&amp;L'!P2*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="17">
+      <c r="Q3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="T3" s="17">
+      <c r="T3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="U3" s="17">
+      <c r="U3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="V3" s="17">
+      <c r="V3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="W3" s="17">
+      <c r="W3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="X3" s="17">
+      <c r="X3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="Y3" s="17">
+      <c r="Y3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="Z3" s="17">
+      <c r="Z3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AA3" s="17">
+      <c r="AA3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AB3" s="17">
+      <c r="AB3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AC3" s="17">
+      <c r="AC3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AD3" s="17">
+      <c r="AD3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AE3" s="17">
+      <c r="AE3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AF3" s="17">
+      <c r="AF3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AG3" s="17">
+      <c r="AG3" s="16">
         <f>P3</f>
         <v/>
       </c>
-      <c r="AH3" s="17">
+      <c r="AH3" s="16">
         <f>P3</f>
         <v/>
       </c>
@@ -7057,135 +7056,135 @@
           <t>Inventories — DIO (days)</t>
         </is>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="15">
         <f>IFERROR('QTR BS'!B4/'QTR P&amp;L'!B3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <f>IFERROR('QTR BS'!C4/'QTR P&amp;L'!C3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="15">
         <f>IFERROR('QTR BS'!D4/'QTR P&amp;L'!D3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="E4" s="16">
+      <c r="E4" s="15">
         <f>IFERROR('QTR BS'!E4/'QTR P&amp;L'!E3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="15">
         <f>IFERROR('QTR BS'!F4/'QTR P&amp;L'!F3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="15">
         <f>IFERROR('QTR BS'!G4/'QTR P&amp;L'!G3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="15">
         <f>IFERROR('QTR BS'!H4/'QTR P&amp;L'!H3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="15">
         <f>IFERROR('QTR BS'!I4/'QTR P&amp;L'!I3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="15">
         <f>IFERROR('QTR BS'!J4/'QTR P&amp;L'!J3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="15">
         <f>IFERROR('QTR BS'!K4/'QTR P&amp;L'!K3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="15">
         <f>IFERROR('QTR BS'!L4/'QTR P&amp;L'!L3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="15">
         <f>IFERROR('QTR BS'!M4/'QTR P&amp;L'!M3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="N4" s="16">
+      <c r="N4" s="15">
         <f>IFERROR('QTR BS'!N4/'QTR P&amp;L'!N3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="O4" s="16">
+      <c r="O4" s="15">
         <f>IFERROR('QTR BS'!O4/'QTR P&amp;L'!O3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="P4" s="16">
+      <c r="P4" s="15">
         <f>IFERROR('QTR BS'!P4/'QTR P&amp;L'!P3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="R4" s="17">
+      <c r="R4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="S4" s="17">
+      <c r="S4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="T4" s="17">
+      <c r="T4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="U4" s="17">
+      <c r="U4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="V4" s="17">
+      <c r="V4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="W4" s="17">
+      <c r="W4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="X4" s="17">
+      <c r="X4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="Y4" s="17">
+      <c r="Y4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="Z4" s="17">
+      <c r="Z4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AA4" s="17">
+      <c r="AA4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AB4" s="17">
+      <c r="AB4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AC4" s="17">
+      <c r="AC4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AD4" s="17">
+      <c r="AD4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AE4" s="17">
+      <c r="AE4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AF4" s="17">
+      <c r="AF4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AG4" s="17">
+      <c r="AG4" s="16">
         <f>P4</f>
         <v/>
       </c>
-      <c r="AH4" s="17">
+      <c r="AH4" s="16">
         <f>P4</f>
         <v/>
       </c>
@@ -7196,135 +7195,135 @@
           <t>Prepaid Expenses — % of Revenue</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <f>IFERROR('QTR BS'!B5/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="12">
         <f>IFERROR('QTR BS'!C5/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <f>IFERROR('QTR BS'!D5/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <f>IFERROR('QTR BS'!E5/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <f>IFERROR('QTR BS'!F5/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="12">
         <f>IFERROR('QTR BS'!G5/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f>IFERROR('QTR BS'!H5/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="12">
         <f>IFERROR('QTR BS'!I5/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="12">
         <f>IFERROR('QTR BS'!J5/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="12">
         <f>IFERROR('QTR BS'!K5/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="12">
         <f>IFERROR('QTR BS'!L5/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="12">
         <f>IFERROR('QTR BS'!M5/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="12">
         <f>IFERROR('QTR BS'!N5/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="12">
         <f>IFERROR('QTR BS'!O5/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="12">
         <f>IFERROR('QTR BS'!P5/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="R5" s="14">
+      <c r="R5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="S5" s="14">
+      <c r="S5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="T5" s="14">
+      <c r="T5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="U5" s="14">
+      <c r="U5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="V5" s="14">
+      <c r="V5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="W5" s="14">
+      <c r="W5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="X5" s="14">
+      <c r="X5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="Y5" s="14">
+      <c r="Y5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="Z5" s="14">
+      <c r="Z5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AA5" s="14">
+      <c r="AA5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AB5" s="14">
+      <c r="AB5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AC5" s="14">
+      <c r="AC5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AD5" s="14">
+      <c r="AD5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AE5" s="14">
+      <c r="AE5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AF5" s="14">
+      <c r="AF5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AG5" s="14">
+      <c r="AG5" s="13">
         <f>P5</f>
         <v/>
       </c>
-      <c r="AH5" s="14">
+      <c r="AH5" s="13">
         <f>P5</f>
         <v/>
       </c>
@@ -7534,75 +7533,75 @@
         <f>'QTR BS'!P8</f>
         <v/>
       </c>
-      <c r="Q7" s="15">
+      <c r="Q7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="R7" s="15">
+      <c r="R7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="S7" s="15">
+      <c r="S7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="T7" s="15">
+      <c r="T7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="U7" s="15">
+      <c r="U7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="V7" s="15">
+      <c r="V7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="W7" s="15">
+      <c r="W7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="X7" s="15">
+      <c r="X7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="Y7" s="15">
+      <c r="Y7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="Z7" s="15">
+      <c r="Z7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AA7" s="15">
+      <c r="AA7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AB7" s="15">
+      <c r="AB7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AC7" s="15">
+      <c r="AC7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AD7" s="15">
+      <c r="AD7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AE7" s="15">
+      <c r="AE7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AF7" s="15">
+      <c r="AF7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AG7" s="15">
+      <c r="AG7" s="14">
         <f>P7</f>
         <v/>
       </c>
-      <c r="AH7" s="15">
+      <c r="AH7" s="14">
         <f>P7</f>
         <v/>
       </c>
@@ -7673,75 +7672,75 @@
         <f>'QTR BS'!P9</f>
         <v/>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="R8" s="15">
+      <c r="R8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="S8" s="15">
+      <c r="S8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="T8" s="15">
+      <c r="T8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="U8" s="15">
+      <c r="U8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="V8" s="15">
+      <c r="V8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="W8" s="15">
+      <c r="W8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="X8" s="15">
+      <c r="X8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="Y8" s="15">
+      <c r="Y8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="Z8" s="15">
+      <c r="Z8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AA8" s="15">
+      <c r="AA8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AB8" s="15">
+      <c r="AB8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AC8" s="15">
+      <c r="AC8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AD8" s="15">
+      <c r="AD8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AE8" s="15">
+      <c r="AE8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AF8" s="15">
+      <c r="AF8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AG8" s="15">
+      <c r="AG8" s="14">
         <f>P8</f>
         <v/>
       </c>
-      <c r="AH8" s="15">
+      <c r="AH8" s="14">
         <f>P8</f>
         <v/>
       </c>
@@ -7752,135 +7751,135 @@
           <t>Other Non-Current Assets — % of Revenue</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="12">
         <f>IFERROR('QTR BS'!B10/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="12">
         <f>IFERROR('QTR BS'!C10/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="12">
         <f>IFERROR('QTR BS'!D10/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="12">
         <f>IFERROR('QTR BS'!E10/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <f>IFERROR('QTR BS'!F10/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="12">
         <f>IFERROR('QTR BS'!G10/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="12">
         <f>IFERROR('QTR BS'!H10/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="12">
         <f>IFERROR('QTR BS'!I10/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="12">
         <f>IFERROR('QTR BS'!J10/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K9" s="13">
+      <c r="K9" s="12">
         <f>IFERROR('QTR BS'!K10/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L9" s="13">
+      <c r="L9" s="12">
         <f>IFERROR('QTR BS'!L10/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M9" s="13">
+      <c r="M9" s="12">
         <f>IFERROR('QTR BS'!M10/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N9" s="13">
+      <c r="N9" s="12">
         <f>IFERROR('QTR BS'!N10/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O9" s="13">
+      <c r="O9" s="12">
         <f>IFERROR('QTR BS'!O10/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P9" s="13">
+      <c r="P9" s="12">
         <f>IFERROR('QTR BS'!P10/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="T9" s="14">
+      <c r="T9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="V9" s="14">
+      <c r="V9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="W9" s="14">
+      <c r="W9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="X9" s="14">
+      <c r="X9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="Y9" s="14">
+      <c r="Y9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="Z9" s="14">
+      <c r="Z9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AA9" s="14">
+      <c r="AA9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AB9" s="14">
+      <c r="AB9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AC9" s="14">
+      <c r="AC9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AD9" s="14">
+      <c r="AD9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AE9" s="14">
+      <c r="AE9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AF9" s="14">
+      <c r="AF9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AG9" s="14">
+      <c r="AG9" s="13">
         <f>P9</f>
         <v/>
       </c>
-      <c r="AH9" s="14">
+      <c r="AH9" s="13">
         <f>P9</f>
         <v/>
       </c>
@@ -7891,135 +7890,135 @@
           <t>Accounts Payable — DPO (days)</t>
         </is>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="15">
         <f>IFERROR('QTR BS'!B12/'QTR P&amp;L'!B3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="15">
         <f>IFERROR('QTR BS'!C12/'QTR P&amp;L'!C3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="D10" s="16">
+      <c r="D10" s="15">
         <f>IFERROR('QTR BS'!D12/'QTR P&amp;L'!D3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="15">
         <f>IFERROR('QTR BS'!E12/'QTR P&amp;L'!E3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="15">
         <f>IFERROR('QTR BS'!F12/'QTR P&amp;L'!F3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="15">
         <f>IFERROR('QTR BS'!G12/'QTR P&amp;L'!G3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="H10" s="16">
+      <c r="H10" s="15">
         <f>IFERROR('QTR BS'!H12/'QTR P&amp;L'!H3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="15">
         <f>IFERROR('QTR BS'!I12/'QTR P&amp;L'!I3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="15">
         <f>IFERROR('QTR BS'!J12/'QTR P&amp;L'!J3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="15">
         <f>IFERROR('QTR BS'!K12/'QTR P&amp;L'!K3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="15">
         <f>IFERROR('QTR BS'!L12/'QTR P&amp;L'!L3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="15">
         <f>IFERROR('QTR BS'!M12/'QTR P&amp;L'!M3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="15">
         <f>IFERROR('QTR BS'!N12/'QTR P&amp;L'!N3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="15">
         <f>IFERROR('QTR BS'!O12/'QTR P&amp;L'!O3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="15">
         <f>IFERROR('QTR BS'!P12/'QTR P&amp;L'!P3*ASSUMPTIONS!$B$2,"")</f>
         <v/>
       </c>
-      <c r="Q10" s="17">
+      <c r="Q10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="R10" s="17">
+      <c r="R10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="S10" s="17">
+      <c r="S10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="T10" s="17">
+      <c r="T10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="U10" s="17">
+      <c r="U10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="V10" s="17">
+      <c r="V10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="W10" s="17">
+      <c r="W10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="X10" s="17">
+      <c r="X10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Y10" s="17">
+      <c r="Y10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="Z10" s="17">
+      <c r="Z10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AA10" s="17">
+      <c r="AA10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AB10" s="17">
+      <c r="AB10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AC10" s="17">
+      <c r="AC10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AD10" s="17">
+      <c r="AD10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AE10" s="17">
+      <c r="AE10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AF10" s="17">
+      <c r="AF10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AG10" s="17">
+      <c r="AG10" s="16">
         <f>P10</f>
         <v/>
       </c>
-      <c r="AH10" s="17">
+      <c r="AH10" s="16">
         <f>P10</f>
         <v/>
       </c>
@@ -8030,135 +8029,135 @@
           <t>Accrued Expenses — % of Revenue</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="12">
         <f>IFERROR('QTR BS'!B13/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="12">
         <f>IFERROR('QTR BS'!C13/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="12">
         <f>IFERROR('QTR BS'!D13/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="12">
         <f>IFERROR('QTR BS'!E13/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <f>IFERROR('QTR BS'!F13/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="12">
         <f>IFERROR('QTR BS'!G13/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H11" s="13">
+      <c r="H11" s="12">
         <f>IFERROR('QTR BS'!H13/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="12">
         <f>IFERROR('QTR BS'!I13/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J11" s="13">
+      <c r="J11" s="12">
         <f>IFERROR('QTR BS'!J13/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K11" s="13">
+      <c r="K11" s="12">
         <f>IFERROR('QTR BS'!K13/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L11" s="13">
+      <c r="L11" s="12">
         <f>IFERROR('QTR BS'!L13/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M11" s="13">
+      <c r="M11" s="12">
         <f>IFERROR('QTR BS'!M13/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N11" s="13">
+      <c r="N11" s="12">
         <f>IFERROR('QTR BS'!N13/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O11" s="13">
+      <c r="O11" s="12">
         <f>IFERROR('QTR BS'!O13/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P11" s="13">
+      <c r="P11" s="12">
         <f>IFERROR('QTR BS'!P13/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q11" s="14">
+      <c r="Q11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="R11" s="14">
+      <c r="R11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="S11" s="14">
+      <c r="S11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="T11" s="14">
+      <c r="T11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="U11" s="14">
+      <c r="U11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="V11" s="14">
+      <c r="V11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="W11" s="14">
+      <c r="W11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="X11" s="14">
+      <c r="X11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="Y11" s="14">
+      <c r="Y11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="Z11" s="14">
+      <c r="Z11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AA11" s="14">
+      <c r="AA11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AB11" s="14">
+      <c r="AB11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AC11" s="14">
+      <c r="AC11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AD11" s="14">
+      <c r="AD11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AE11" s="14">
+      <c r="AE11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AF11" s="14">
+      <c r="AF11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AG11" s="14">
+      <c r="AG11" s="13">
         <f>P11</f>
         <v/>
       </c>
-      <c r="AH11" s="14">
+      <c r="AH11" s="13">
         <f>P11</f>
         <v/>
       </c>
@@ -8229,75 +8228,75 @@
         <f>'QTR BS'!P14</f>
         <v/>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="R12" s="15">
+      <c r="R12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="U12" s="15">
+      <c r="U12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="V12" s="15">
+      <c r="V12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="W12" s="15">
+      <c r="W12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="X12" s="15">
+      <c r="X12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="Y12" s="15">
+      <c r="Y12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="Z12" s="15">
+      <c r="Z12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AA12" s="15">
+      <c r="AA12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AB12" s="15">
+      <c r="AB12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AC12" s="15">
+      <c r="AC12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AD12" s="15">
+      <c r="AD12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AE12" s="15">
+      <c r="AE12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AF12" s="15">
+      <c r="AF12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AG12" s="15">
+      <c r="AG12" s="14">
         <f>P12</f>
         <v/>
       </c>
-      <c r="AH12" s="15">
+      <c r="AH12" s="14">
         <f>P12</f>
         <v/>
       </c>
@@ -8368,75 +8367,75 @@
         <f>'QTR BS'!P16</f>
         <v/>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="R13" s="15">
+      <c r="R13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="U13" s="15">
+      <c r="U13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="V13" s="15">
+      <c r="V13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="W13" s="15">
+      <c r="W13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="X13" s="15">
+      <c r="X13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="Y13" s="15">
+      <c r="Y13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="Z13" s="15">
+      <c r="Z13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AA13" s="15">
+      <c r="AA13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AB13" s="15">
+      <c r="AB13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AC13" s="15">
+      <c r="AC13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AD13" s="15">
+      <c r="AD13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AE13" s="15">
+      <c r="AE13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AF13" s="15">
+      <c r="AF13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AG13" s="15">
+      <c r="AG13" s="14">
         <f>P13</f>
         <v/>
       </c>
-      <c r="AH13" s="15">
+      <c r="AH13" s="14">
         <f>P13</f>
         <v/>
       </c>
@@ -8507,75 +8506,75 @@
         <f>'QTR BS'!P17</f>
         <v/>
       </c>
-      <c r="Q14" s="15">
+      <c r="Q14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="R14" s="15">
+      <c r="R14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="U14" s="15">
+      <c r="U14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="V14" s="15">
+      <c r="V14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="W14" s="15">
+      <c r="W14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="X14" s="15">
+      <c r="X14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="Y14" s="15">
+      <c r="Y14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="Z14" s="15">
+      <c r="Z14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AA14" s="15">
+      <c r="AA14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AB14" s="15">
+      <c r="AB14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AC14" s="15">
+      <c r="AC14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AD14" s="15">
+      <c r="AD14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AE14" s="15">
+      <c r="AE14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AF14" s="15">
+      <c r="AF14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AG14" s="15">
+      <c r="AG14" s="14">
         <f>P14</f>
         <v/>
       </c>
-      <c r="AH14" s="15">
+      <c r="AH14" s="14">
         <f>P14</f>
         <v/>
       </c>
@@ -8586,135 +8585,135 @@
           <t>Other Non-Current Liabilities — % of Revenue</t>
         </is>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="12">
         <f>IFERROR('QTR BS'!B18/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="12">
         <f>IFERROR('QTR BS'!C18/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="12">
         <f>IFERROR('QTR BS'!D18/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="12">
         <f>IFERROR('QTR BS'!E18/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="12">
         <f>IFERROR('QTR BS'!F18/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="12">
         <f>IFERROR('QTR BS'!G18/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H15" s="13">
+      <c r="H15" s="12">
         <f>IFERROR('QTR BS'!H18/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="12">
         <f>IFERROR('QTR BS'!I18/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="12">
         <f>IFERROR('QTR BS'!J18/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K15" s="13">
+      <c r="K15" s="12">
         <f>IFERROR('QTR BS'!K18/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L15" s="13">
+      <c r="L15" s="12">
         <f>IFERROR('QTR BS'!L18/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M15" s="13">
+      <c r="M15" s="12">
         <f>IFERROR('QTR BS'!M18/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N15" s="13">
+      <c r="N15" s="12">
         <f>IFERROR('QTR BS'!N18/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O15" s="13">
+      <c r="O15" s="12">
         <f>IFERROR('QTR BS'!O18/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P15" s="13">
+      <c r="P15" s="12">
         <f>IFERROR('QTR BS'!P18/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q15" s="14">
+      <c r="Q15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="R15" s="14">
+      <c r="R15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="S15" s="14">
+      <c r="S15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="T15" s="14">
+      <c r="T15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="U15" s="14">
+      <c r="U15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="V15" s="14">
+      <c r="V15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="W15" s="14">
+      <c r="W15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="X15" s="14">
+      <c r="X15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="Y15" s="14">
+      <c r="Y15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="Z15" s="14">
+      <c r="Z15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AA15" s="14">
+      <c r="AA15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AB15" s="14">
+      <c r="AB15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AC15" s="14">
+      <c r="AC15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AD15" s="14">
+      <c r="AD15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AE15" s="14">
+      <c r="AE15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AF15" s="14">
+      <c r="AF15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AG15" s="14">
+      <c r="AG15" s="13">
         <f>P15</f>
         <v/>
       </c>
-      <c r="AH15" s="14">
+      <c r="AH15" s="13">
         <f>P15</f>
         <v/>
       </c>
@@ -8785,75 +8784,75 @@
         <f>'QTR BS'!P20</f>
         <v/>
       </c>
-      <c r="Q16" s="15">
+      <c r="Q16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="R16" s="15">
+      <c r="R16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="U16" s="15">
+      <c r="U16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="V16" s="15">
+      <c r="V16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="W16" s="15">
+      <c r="W16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="X16" s="15">
+      <c r="X16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="Y16" s="15">
+      <c r="Y16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="Z16" s="15">
+      <c r="Z16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AA16" s="15">
+      <c r="AA16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AB16" s="15">
+      <c r="AB16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AC16" s="15">
+      <c r="AC16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AD16" s="15">
+      <c r="AD16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AE16" s="15">
+      <c r="AE16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AF16" s="15">
+      <c r="AF16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AG16" s="15">
+      <c r="AG16" s="14">
         <f>P16</f>
         <v/>
       </c>
-      <c r="AH16" s="15">
+      <c r="AH16" s="14">
         <f>P16</f>
         <v/>
       </c>
@@ -8924,75 +8923,75 @@
         <f>'QTR BS'!P21</f>
         <v/>
       </c>
-      <c r="Q17" s="15">
+      <c r="Q17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="R17" s="15">
+      <c r="R17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="U17" s="15">
+      <c r="U17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="V17" s="15">
+      <c r="V17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="W17" s="15">
+      <c r="W17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="X17" s="15">
+      <c r="X17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="Y17" s="15">
+      <c r="Y17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="Z17" s="15">
+      <c r="Z17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AA17" s="15">
+      <c r="AA17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AB17" s="15">
+      <c r="AB17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AC17" s="15">
+      <c r="AC17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AD17" s="15">
+      <c r="AD17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AE17" s="15">
+      <c r="AE17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AF17" s="15">
+      <c r="AF17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AG17" s="15">
+      <c r="AG17" s="14">
         <f>P17</f>
         <v/>
       </c>
-      <c r="AH17" s="15">
+      <c r="AH17" s="14">
         <f>P17</f>
         <v/>
       </c>
@@ -9202,58 +9201,58 @@
         <f>'QTR BS'!P23</f>
         <v/>
       </c>
-      <c r="Q19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="15" t="n">
+      <c r="Q19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9462,75 +9461,75 @@
         <f>'QTR BS'!P25</f>
         <v/>
       </c>
-      <c r="Q21" s="15">
+      <c r="Q21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="R21" s="15">
+      <c r="R21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="S21" s="15">
+      <c r="S21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="T21" s="15">
+      <c r="T21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="U21" s="15">
+      <c r="U21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="V21" s="15">
+      <c r="V21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="W21" s="15">
+      <c r="W21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="X21" s="15">
+      <c r="X21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="Y21" s="15">
+      <c r="Y21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="Z21" s="15">
+      <c r="Z21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AA21" s="15">
+      <c r="AA21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AB21" s="15">
+      <c r="AB21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AC21" s="15">
+      <c r="AC21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AD21" s="15">
+      <c r="AD21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AE21" s="15">
+      <c r="AE21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AF21" s="15">
+      <c r="AF21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AG21" s="15">
+      <c r="AG21" s="14">
         <f>P21</f>
         <v/>
       </c>
-      <c r="AH21" s="15">
+      <c r="AH21" s="14">
         <f>P21</f>
         <v/>
       </c>
@@ -9740,75 +9739,75 @@
         <f>'QTR BS'!P27</f>
         <v/>
       </c>
-      <c r="Q23" s="15">
+      <c r="Q23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="R23" s="15">
+      <c r="R23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="U23" s="15">
+      <c r="U23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="V23" s="15">
+      <c r="V23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="W23" s="15">
+      <c r="W23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="X23" s="15">
+      <c r="X23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="Y23" s="15">
+      <c r="Y23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="Z23" s="15">
+      <c r="Z23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AA23" s="15">
+      <c r="AA23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AB23" s="15">
+      <c r="AB23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AC23" s="15">
+      <c r="AC23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AD23" s="15">
+      <c r="AD23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AE23" s="15">
+      <c r="AE23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AF23" s="15">
+      <c r="AF23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AG23" s="15">
+      <c r="AG23" s="14">
         <f>P23</f>
         <v/>
       </c>
-      <c r="AH23" s="15">
+      <c r="AH23" s="14">
         <f>P23</f>
         <v/>
       </c>
@@ -10210,147 +10209,147 @@
           <t>Depreciation &amp; Amortization — % of Revenue</t>
         </is>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="12">
         <f>IFERROR('QTR CF'!B3/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="12">
         <f>IFERROR('QTR CF'!C3/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="12">
         <f>IFERROR('QTR CF'!D3/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="12">
         <f>IFERROR('QTR CF'!E3/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <f>IFERROR('QTR CF'!F3/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="12">
         <f>IFERROR('QTR CF'!G3/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <f>IFERROR('QTR CF'!H3/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="12">
         <f>IFERROR('QTR CF'!I3/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="12">
         <f>IFERROR('QTR CF'!J3/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="12">
         <f>IFERROR('QTR CF'!K3/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="12">
         <f>IFERROR('QTR CF'!L3/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M3" s="13">
+      <c r="M3" s="12">
         <f>IFERROR('QTR CF'!M3/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N3" s="13">
+      <c r="N3" s="12">
         <f>IFERROR('QTR CF'!N3/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="12">
         <f>IFERROR('QTR CF'!O3/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P3" s="13">
+      <c r="P3" s="12">
         <f>IFERROR('QTR CF'!P3/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q3" s="13">
+      <c r="Q3" s="12">
         <f>IFERROR('QTR CF'!Q3/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R3" s="13">
+      <c r="R3" s="12">
         <f>IFERROR('QTR CF'!R3/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S3" s="13">
+      <c r="S3" s="12">
         <f>IFERROR('QTR CF'!S3/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="U3" s="14">
+      <c r="U3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="V3" s="14">
+      <c r="V3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="W3" s="14">
+      <c r="W3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="X3" s="14">
+      <c r="X3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="Z3" s="14">
+      <c r="Z3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AA3" s="14">
+      <c r="AA3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AB3" s="14">
+      <c r="AB3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AC3" s="14">
+      <c r="AC3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AD3" s="14">
+      <c r="AD3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AE3" s="14">
+      <c r="AE3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AF3" s="14">
+      <c r="AF3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AG3" s="14">
+      <c r="AG3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AH3" s="14">
+      <c r="AH3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AI3" s="14">
+      <c r="AI3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AJ3" s="14">
+      <c r="AJ3" s="13">
         <f>S3</f>
         <v/>
       </c>
-      <c r="AK3" s="14">
+      <c r="AK3" s="13">
         <f>S3</f>
         <v/>
       </c>
@@ -10361,147 +10360,147 @@
           <t>Stock-Based Compensation — % of Revenue</t>
         </is>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <f>IFERROR('QTR CF'!B4/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="12">
         <f>IFERROR('QTR CF'!C4/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="12">
         <f>IFERROR('QTR CF'!D4/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="12">
         <f>IFERROR('QTR CF'!E4/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <f>IFERROR('QTR CF'!F4/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="12">
         <f>IFERROR('QTR CF'!G4/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f>IFERROR('QTR CF'!H4/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="12">
         <f>IFERROR('QTR CF'!I4/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="12">
         <f>IFERROR('QTR CF'!J4/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="12">
         <f>IFERROR('QTR CF'!K4/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <f>IFERROR('QTR CF'!L4/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <f>IFERROR('QTR CF'!M4/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <f>IFERROR('QTR CF'!N4/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <f>IFERROR('QTR CF'!O4/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="12">
         <f>IFERROR('QTR CF'!P4/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="12">
         <f>IFERROR('QTR CF'!Q4/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="12">
         <f>IFERROR('QTR CF'!R4/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="12">
         <f>IFERROR('QTR CF'!S4/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T4" s="14">
+      <c r="T4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="U4" s="14">
+      <c r="U4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="V4" s="14">
+      <c r="V4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="W4" s="14">
+      <c r="W4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="Z4" s="14">
+      <c r="Z4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AA4" s="14">
+      <c r="AA4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AB4" s="14">
+      <c r="AB4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AC4" s="14">
+      <c r="AC4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AD4" s="14">
+      <c r="AD4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AE4" s="14">
+      <c r="AE4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AF4" s="14">
+      <c r="AF4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AG4" s="14">
+      <c r="AG4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AH4" s="14">
+      <c r="AH4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AI4" s="14">
+      <c r="AI4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AJ4" s="14">
+      <c r="AJ4" s="13">
         <f>S4</f>
         <v/>
       </c>
-      <c r="AK4" s="14">
+      <c r="AK4" s="13">
         <f>S4</f>
         <v/>
       </c>
@@ -10584,58 +10583,58 @@
         <f>'QTR CF'!S5</f>
         <v/>
       </c>
-      <c r="T5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ5" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" s="15" t="n">
+      <c r="T5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10717,58 +10716,58 @@
         <f>'QTR CF'!S6</f>
         <v/>
       </c>
-      <c r="T6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" s="15" t="n">
+      <c r="T6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10850,58 +10849,58 @@
         <f>'QTR CF'!S7</f>
         <v/>
       </c>
-      <c r="T7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="15" t="n">
+      <c r="T7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11436,58 +11435,58 @@
         <f>'QTR CF'!S11</f>
         <v/>
       </c>
-      <c r="T11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" s="15" t="n">
+      <c r="T11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -11648,147 +11647,147 @@
           <t>Purchase of PP&amp;E — % of Revenue</t>
         </is>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="12">
         <f>IFERROR('QTR CF'!B14/'QTR P&amp;L'!B2,"")</f>
         <v/>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="12">
         <f>IFERROR('QTR CF'!C14/'QTR P&amp;L'!C2,"")</f>
         <v/>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="12">
         <f>IFERROR('QTR CF'!D14/'QTR P&amp;L'!D2,"")</f>
         <v/>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="12">
         <f>IFERROR('QTR CF'!E14/'QTR P&amp;L'!E2,"")</f>
         <v/>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <f>IFERROR('QTR CF'!F14/'QTR P&amp;L'!F2,"")</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="12">
         <f>IFERROR('QTR CF'!G14/'QTR P&amp;L'!G2,"")</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <f>IFERROR('QTR CF'!H14/'QTR P&amp;L'!H2,"")</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <f>IFERROR('QTR CF'!I14/'QTR P&amp;L'!I2,"")</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <f>IFERROR('QTR CF'!J14/'QTR P&amp;L'!J2,"")</f>
         <v/>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <f>IFERROR('QTR CF'!K14/'QTR P&amp;L'!K2,"")</f>
         <v/>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="12">
         <f>IFERROR('QTR CF'!L14/'QTR P&amp;L'!L2,"")</f>
         <v/>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <f>IFERROR('QTR CF'!M14/'QTR P&amp;L'!M2,"")</f>
         <v/>
       </c>
-      <c r="N13" s="13">
+      <c r="N13" s="12">
         <f>IFERROR('QTR CF'!N14/'QTR P&amp;L'!N2,"")</f>
         <v/>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="12">
         <f>IFERROR('QTR CF'!O14/'QTR P&amp;L'!O2,"")</f>
         <v/>
       </c>
-      <c r="P13" s="13">
+      <c r="P13" s="12">
         <f>IFERROR('QTR CF'!P14/'QTR P&amp;L'!P2,"")</f>
         <v/>
       </c>
-      <c r="Q13" s="13">
+      <c r="Q13" s="12">
         <f>IFERROR('QTR CF'!Q14/'QTR P&amp;L'!Q2,"")</f>
         <v/>
       </c>
-      <c r="R13" s="13">
+      <c r="R13" s="12">
         <f>IFERROR('QTR CF'!R14/'QTR P&amp;L'!R2,"")</f>
         <v/>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="12">
         <f>IFERROR('QTR CF'!S14/'QTR P&amp;L'!S2,"")</f>
         <v/>
       </c>
-      <c r="T13" s="14">
+      <c r="T13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="U13" s="14">
+      <c r="U13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="V13" s="14">
+      <c r="V13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="W13" s="14">
+      <c r="W13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="X13" s="14">
+      <c r="X13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="Y13" s="14">
+      <c r="Y13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="Z13" s="14">
+      <c r="Z13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AA13" s="14">
+      <c r="AA13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AB13" s="14">
+      <c r="AB13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AC13" s="14">
+      <c r="AC13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AD13" s="14">
+      <c r="AD13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AE13" s="14">
+      <c r="AE13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AF13" s="14">
+      <c r="AF13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AG13" s="14">
+      <c r="AG13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AH13" s="14">
+      <c r="AH13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AI13" s="14">
+      <c r="AI13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AJ13" s="14">
+      <c r="AJ13" s="13">
         <f>S13</f>
         <v/>
       </c>
-      <c r="AK13" s="14">
+      <c r="AK13" s="13">
         <f>S13</f>
         <v/>
       </c>
@@ -11871,58 +11870,58 @@
         <f>'QTR CF'!S15</f>
         <v/>
       </c>
-      <c r="T14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" s="15" t="n">
+      <c r="T14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12004,58 +12003,58 @@
         <f>'QTR CF'!S16</f>
         <v/>
       </c>
-      <c r="T15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="15" t="n">
+      <c r="T15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12137,58 +12136,58 @@
         <f>'QTR CF'!S17</f>
         <v/>
       </c>
-      <c r="T16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" s="15" t="n">
+      <c r="T16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12270,58 +12269,58 @@
         <f>'QTR CF'!S18</f>
         <v/>
       </c>
-      <c r="T17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" s="15" t="n">
+      <c r="T17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12331,147 +12330,147 @@
           <t>Common Dividends — % of Net Income</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="12">
         <f>IFERROR('QTR CF'!B20/'QTR P&amp;L'!B12,"")</f>
         <v/>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="12">
         <f>IFERROR('QTR CF'!C20/'QTR P&amp;L'!C12,"")</f>
         <v/>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <f>IFERROR('QTR CF'!D20/'QTR P&amp;L'!D12,"")</f>
         <v/>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f>IFERROR('QTR CF'!E20/'QTR P&amp;L'!E12,"")</f>
         <v/>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <f>IFERROR('QTR CF'!F20/'QTR P&amp;L'!F12,"")</f>
         <v/>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <f>IFERROR('QTR CF'!G20/'QTR P&amp;L'!G12,"")</f>
         <v/>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="12">
         <f>IFERROR('QTR CF'!H20/'QTR P&amp;L'!H12,"")</f>
         <v/>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f>IFERROR('QTR CF'!I20/'QTR P&amp;L'!I12,"")</f>
         <v/>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="12">
         <f>IFERROR('QTR CF'!J20/'QTR P&amp;L'!J12,"")</f>
         <v/>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="12">
         <f>IFERROR('QTR CF'!K20/'QTR P&amp;L'!K12,"")</f>
         <v/>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="12">
         <f>IFERROR('QTR CF'!L20/'QTR P&amp;L'!L12,"")</f>
         <v/>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f>IFERROR('QTR CF'!M20/'QTR P&amp;L'!M12,"")</f>
         <v/>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="12">
         <f>IFERROR('QTR CF'!N20/'QTR P&amp;L'!N12,"")</f>
         <v/>
       </c>
-      <c r="O18" s="13">
+      <c r="O18" s="12">
         <f>IFERROR('QTR CF'!O20/'QTR P&amp;L'!O12,"")</f>
         <v/>
       </c>
-      <c r="P18" s="13">
+      <c r="P18" s="12">
         <f>IFERROR('QTR CF'!P20/'QTR P&amp;L'!P12,"")</f>
         <v/>
       </c>
-      <c r="Q18" s="13">
+      <c r="Q18" s="12">
         <f>IFERROR('QTR CF'!Q20/'QTR P&amp;L'!Q12,"")</f>
         <v/>
       </c>
-      <c r="R18" s="13">
+      <c r="R18" s="12">
         <f>IFERROR('QTR CF'!R20/'QTR P&amp;L'!R12,"")</f>
         <v/>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="12">
         <f>IFERROR('QTR CF'!S20/'QTR P&amp;L'!S12,"")</f>
         <v/>
       </c>
-      <c r="T18" s="14">
+      <c r="T18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="U18" s="14">
+      <c r="U18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="V18" s="14">
+      <c r="V18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="W18" s="14">
+      <c r="W18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="X18" s="14">
+      <c r="X18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="Y18" s="14">
+      <c r="Y18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="Z18" s="14">
+      <c r="Z18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AA18" s="14">
+      <c r="AA18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AB18" s="14">
+      <c r="AB18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AC18" s="14">
+      <c r="AC18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AD18" s="14">
+      <c r="AD18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AE18" s="14">
+      <c r="AE18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AF18" s="14">
+      <c r="AF18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AG18" s="14">
+      <c r="AG18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AH18" s="14">
+      <c r="AH18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AI18" s="14">
+      <c r="AI18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AJ18" s="14">
+      <c r="AJ18" s="13">
         <f>S18</f>
         <v/>
       </c>
-      <c r="AK18" s="14">
+      <c r="AK18" s="13">
         <f>S18</f>
         <v/>
       </c>
@@ -12554,58 +12553,58 @@
         <f>'QTR CF'!S21</f>
         <v/>
       </c>
-      <c r="T19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="15" t="n">
+      <c r="T19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12687,58 +12686,58 @@
         <f>'QTR CF'!S22</f>
         <v/>
       </c>
-      <c r="T20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="15" t="n">
+      <c r="T20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12820,58 +12819,58 @@
         <f>'QTR CF'!S23</f>
         <v/>
       </c>
-      <c r="T21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="15" t="n">
+      <c r="T21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12953,58 +12952,58 @@
         <f>'QTR CF'!S24</f>
         <v/>
       </c>
-      <c r="T22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="15" t="n">
+      <c r="T22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13086,58 +13085,58 @@
         <f>'QTR CF'!S25</f>
         <v/>
       </c>
-      <c r="T23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="15" t="n">
+      <c r="T23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13219,58 +13218,58 @@
         <f>'QTR CF'!S26</f>
         <v/>
       </c>
-      <c r="T24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="15" t="n">
+      <c r="T24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13352,58 +13351,58 @@
         <f>'QTR CF'!S27</f>
         <v/>
       </c>
-      <c r="T25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="15" t="n">
+      <c r="T25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13485,75 +13484,75 @@
         <f>'QTR CF'!S29</f>
         <v/>
       </c>
-      <c r="T26" s="15">
+      <c r="T26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="U26" s="15">
+      <c r="U26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="V26" s="15">
+      <c r="V26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="W26" s="15">
+      <c r="W26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="X26" s="15">
+      <c r="X26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="Y26" s="15">
+      <c r="Y26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="Z26" s="15">
+      <c r="Z26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AA26" s="15">
+      <c r="AA26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AB26" s="15">
+      <c r="AB26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AC26" s="15">
+      <c r="AC26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AD26" s="15">
+      <c r="AD26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AE26" s="15">
+      <c r="AE26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AF26" s="15">
+      <c r="AF26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AG26" s="15">
+      <c r="AG26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AH26" s="15">
+      <c r="AH26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AI26" s="15">
+      <c r="AI26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AJ26" s="15">
+      <c r="AJ26" s="14">
         <f>S26</f>
         <v/>
       </c>
-      <c r="AK26" s="15">
+      <c r="AK26" s="14">
         <f>S26</f>
         <v/>
       </c>
@@ -13615,32 +13614,32 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>FY2025E</t>
+          <t>FY2026E</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>FY2026E</t>
+          <t>FY2027E</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>FY2027E</t>
+          <t>FY2028E</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>FY2028E</t>
+          <t>FY2029E</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>FY2029E</t>
+          <t>FY2030E</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>FY2030E</t>
+          <t>FY2031E</t>
         </is>
       </c>
     </row>
@@ -13665,30 +13664,27 @@
       <c r="F2" s="4" t="n">
         <v>84284</v>
       </c>
-      <c r="G2" s="5">
-        <f>'QTR P&amp;L'!N2+'QTR P&amp;L'!O2+'QTR P&amp;L'!P2+'QTR P&amp;L'!Q2</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2" s="11">
         <f>'QTR P&amp;L'!R2+'QTR P&amp;L'!S2+'QTR P&amp;L'!T2+'QTR P&amp;L'!U2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="H2" s="11">
         <f>'QTR P&amp;L'!V2+'QTR P&amp;L'!W2+'QTR P&amp;L'!X2+'QTR P&amp;L'!Y2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="I2" s="11">
         <f>'QTR P&amp;L'!Z2+'QTR P&amp;L'!AA2+'QTR P&amp;L'!AB2+'QTR P&amp;L'!AC2</f>
         <v/>
       </c>
-      <c r="K2" s="5">
+      <c r="J2" s="11">
         <f>'QTR P&amp;L'!AD2+'QTR P&amp;L'!AE2+'QTR P&amp;L'!AF2+'QTR P&amp;L'!AG2</f>
         <v/>
       </c>
-      <c r="L2" s="5">
+      <c r="K2" s="11">
         <f>'QTR P&amp;L'!AH2+'QTR P&amp;L'!AI2+'QTR P&amp;L'!AJ2+'QTR P&amp;L'!AK2</f>
         <v/>
       </c>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -13711,30 +13707,27 @@
       <c r="F3" s="4" t="n">
         <v>-41164</v>
       </c>
-      <c r="G3" s="5">
-        <f>'QTR P&amp;L'!N3+'QTR P&amp;L'!O3+'QTR P&amp;L'!P3+'QTR P&amp;L'!Q3</f>
-        <v/>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="11">
         <f>'QTR P&amp;L'!R3+'QTR P&amp;L'!S3+'QTR P&amp;L'!T3+'QTR P&amp;L'!U3</f>
         <v/>
       </c>
-      <c r="I3" s="5">
+      <c r="H3" s="11">
         <f>'QTR P&amp;L'!V3+'QTR P&amp;L'!W3+'QTR P&amp;L'!X3+'QTR P&amp;L'!Y3</f>
         <v/>
       </c>
-      <c r="J3" s="5">
+      <c r="I3" s="11">
         <f>'QTR P&amp;L'!Z3+'QTR P&amp;L'!AA3+'QTR P&amp;L'!AB3+'QTR P&amp;L'!AC3</f>
         <v/>
       </c>
-      <c r="K3" s="5">
+      <c r="J3" s="11">
         <f>'QTR P&amp;L'!AD3+'QTR P&amp;L'!AE3+'QTR P&amp;L'!AF3+'QTR P&amp;L'!AG3</f>
         <v/>
       </c>
-      <c r="L3" s="5">
+      <c r="K3" s="11">
         <f>'QTR P&amp;L'!AH3+'QTR P&amp;L'!AI3+'QTR P&amp;L'!AJ3+'QTR P&amp;L'!AK3</f>
         <v/>
       </c>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -13808,30 +13801,27 @@
       <c r="F5" s="4" t="n">
         <v>-22669</v>
       </c>
-      <c r="G5" s="5">
-        <f>'QTR P&amp;L'!N5+'QTR P&amp;L'!O5+'QTR P&amp;L'!P5+'QTR P&amp;L'!Q5</f>
-        <v/>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="11">
         <f>'QTR P&amp;L'!R5+'QTR P&amp;L'!S5+'QTR P&amp;L'!T5+'QTR P&amp;L'!U5</f>
         <v/>
       </c>
-      <c r="I5" s="5">
+      <c r="H5" s="11">
         <f>'QTR P&amp;L'!V5+'QTR P&amp;L'!W5+'QTR P&amp;L'!X5+'QTR P&amp;L'!Y5</f>
         <v/>
       </c>
-      <c r="J5" s="5">
+      <c r="I5" s="11">
         <f>'QTR P&amp;L'!Z5+'QTR P&amp;L'!AA5+'QTR P&amp;L'!AB5+'QTR P&amp;L'!AC5</f>
         <v/>
       </c>
-      <c r="K5" s="5">
+      <c r="J5" s="11">
         <f>'QTR P&amp;L'!AD5+'QTR P&amp;L'!AE5+'QTR P&amp;L'!AF5+'QTR P&amp;L'!AG5</f>
         <v/>
       </c>
-      <c r="L5" s="5">
+      <c r="K5" s="11">
         <f>'QTR P&amp;L'!AH5+'QTR P&amp;L'!AI5+'QTR P&amp;L'!AJ5+'QTR P&amp;L'!AK5</f>
         <v/>
       </c>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -13854,30 +13844,27 @@
       <c r="F6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="5">
-        <f>'QTR P&amp;L'!N6+'QTR P&amp;L'!O6+'QTR P&amp;L'!P6+'QTR P&amp;L'!Q6</f>
-        <v/>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6" s="11">
         <f>'QTR P&amp;L'!R6+'QTR P&amp;L'!S6+'QTR P&amp;L'!T6+'QTR P&amp;L'!U6</f>
         <v/>
       </c>
-      <c r="I6" s="5">
+      <c r="H6" s="11">
         <f>'QTR P&amp;L'!V6+'QTR P&amp;L'!W6+'QTR P&amp;L'!X6+'QTR P&amp;L'!Y6</f>
         <v/>
       </c>
-      <c r="J6" s="5">
+      <c r="I6" s="11">
         <f>'QTR P&amp;L'!Z6+'QTR P&amp;L'!AA6+'QTR P&amp;L'!AB6+'QTR P&amp;L'!AC6</f>
         <v/>
       </c>
-      <c r="K6" s="5">
+      <c r="J6" s="11">
         <f>'QTR P&amp;L'!AD6+'QTR P&amp;L'!AE6+'QTR P&amp;L'!AF6+'QTR P&amp;L'!AG6</f>
         <v/>
       </c>
-      <c r="L6" s="5">
+      <c r="K6" s="11">
         <f>'QTR P&amp;L'!AH6+'QTR P&amp;L'!AI6+'QTR P&amp;L'!AJ6+'QTR P&amp;L'!AK6</f>
         <v/>
       </c>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -13951,30 +13938,27 @@
       <c r="F8" s="4" t="n">
         <v>-438</v>
       </c>
-      <c r="G8" s="5">
-        <f>'QTR P&amp;L'!N8+'QTR P&amp;L'!O8+'QTR P&amp;L'!P8+'QTR P&amp;L'!Q8</f>
-        <v/>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8" s="11">
         <f>'QTR P&amp;L'!R8+'QTR P&amp;L'!S8+'QTR P&amp;L'!T8+'QTR P&amp;L'!U8</f>
         <v/>
       </c>
-      <c r="I8" s="5">
+      <c r="H8" s="11">
         <f>'QTR P&amp;L'!V8+'QTR P&amp;L'!W8+'QTR P&amp;L'!X8+'QTR P&amp;L'!Y8</f>
         <v/>
       </c>
-      <c r="J8" s="5">
+      <c r="I8" s="11">
         <f>'QTR P&amp;L'!Z8+'QTR P&amp;L'!AA8+'QTR P&amp;L'!AB8+'QTR P&amp;L'!AC8</f>
         <v/>
       </c>
-      <c r="K8" s="5">
+      <c r="J8" s="11">
         <f>'QTR P&amp;L'!AD8+'QTR P&amp;L'!AE8+'QTR P&amp;L'!AF8+'QTR P&amp;L'!AG8</f>
         <v/>
       </c>
-      <c r="L8" s="5">
+      <c r="K8" s="11">
         <f>'QTR P&amp;L'!AH8+'QTR P&amp;L'!AI8+'QTR P&amp;L'!AJ8+'QTR P&amp;L'!AK8</f>
         <v/>
       </c>
+      <c r="L8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -13997,30 +13981,27 @@
       <c r="F9" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="G9" s="5">
-        <f>'QTR P&amp;L'!N9+'QTR P&amp;L'!O9+'QTR P&amp;L'!P9+'QTR P&amp;L'!Q9</f>
-        <v/>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="11">
         <f>'QTR P&amp;L'!R9+'QTR P&amp;L'!S9+'QTR P&amp;L'!T9+'QTR P&amp;L'!U9</f>
         <v/>
       </c>
-      <c r="I9" s="5">
+      <c r="H9" s="11">
         <f>'QTR P&amp;L'!V9+'QTR P&amp;L'!W9+'QTR P&amp;L'!X9+'QTR P&amp;L'!Y9</f>
         <v/>
       </c>
-      <c r="J9" s="5">
+      <c r="I9" s="11">
         <f>'QTR P&amp;L'!Z9+'QTR P&amp;L'!AA9+'QTR P&amp;L'!AB9+'QTR P&amp;L'!AC9</f>
         <v/>
       </c>
-      <c r="K9" s="5">
+      <c r="J9" s="11">
         <f>'QTR P&amp;L'!AD9+'QTR P&amp;L'!AE9+'QTR P&amp;L'!AF9+'QTR P&amp;L'!AG9</f>
         <v/>
       </c>
-      <c r="L9" s="5">
+      <c r="K9" s="11">
         <f>'QTR P&amp;L'!AH9+'QTR P&amp;L'!AI9+'QTR P&amp;L'!AJ9+'QTR P&amp;L'!AK9</f>
         <v/>
       </c>
+      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -14094,30 +14075,27 @@
       <c r="F11" s="4" t="n">
         <v>-4102</v>
       </c>
-      <c r="G11" s="5">
-        <f>'QTR P&amp;L'!N11+'QTR P&amp;L'!O11+'QTR P&amp;L'!P11+'QTR P&amp;L'!Q11</f>
-        <v/>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11" s="11">
         <f>'QTR P&amp;L'!R11+'QTR P&amp;L'!S11+'QTR P&amp;L'!T11+'QTR P&amp;L'!U11</f>
         <v/>
       </c>
-      <c r="I11" s="5">
+      <c r="H11" s="11">
         <f>'QTR P&amp;L'!V11+'QTR P&amp;L'!W11+'QTR P&amp;L'!X11+'QTR P&amp;L'!Y11</f>
         <v/>
       </c>
-      <c r="J11" s="5">
+      <c r="I11" s="11">
         <f>'QTR P&amp;L'!Z11+'QTR P&amp;L'!AA11+'QTR P&amp;L'!AB11+'QTR P&amp;L'!AC11</f>
         <v/>
       </c>
-      <c r="K11" s="5">
+      <c r="J11" s="11">
         <f>'QTR P&amp;L'!AD11+'QTR P&amp;L'!AE11+'QTR P&amp;L'!AF11+'QTR P&amp;L'!AG11</f>
         <v/>
       </c>
-      <c r="L11" s="5">
+      <c r="K11" s="11">
         <f>'QTR P&amp;L'!AH11+'QTR P&amp;L'!AI11+'QTR P&amp;L'!AJ11+'QTR P&amp;L'!AK11</f>
         <v/>
       </c>
+      <c r="L11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -14191,30 +14169,27 @@
       <c r="F13" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="G13" s="5">
-        <f>'QTR P&amp;L'!N13+'QTR P&amp;L'!O13+'QTR P&amp;L'!P13+'QTR P&amp;L'!Q13</f>
-        <v/>
-      </c>
-      <c r="H13" s="5">
+      <c r="G13" s="11">
         <f>'QTR P&amp;L'!R13+'QTR P&amp;L'!S13+'QTR P&amp;L'!T13+'QTR P&amp;L'!U13</f>
         <v/>
       </c>
-      <c r="I13" s="5">
+      <c r="H13" s="11">
         <f>'QTR P&amp;L'!V13+'QTR P&amp;L'!W13+'QTR P&amp;L'!X13+'QTR P&amp;L'!Y13</f>
         <v/>
       </c>
-      <c r="J13" s="5">
+      <c r="I13" s="11">
         <f>'QTR P&amp;L'!Z13+'QTR P&amp;L'!AA13+'QTR P&amp;L'!AB13+'QTR P&amp;L'!AC13</f>
         <v/>
       </c>
-      <c r="K13" s="5">
+      <c r="J13" s="11">
         <f>'QTR P&amp;L'!AD13+'QTR P&amp;L'!AE13+'QTR P&amp;L'!AF13+'QTR P&amp;L'!AG13</f>
         <v/>
       </c>
-      <c r="L13" s="5">
+      <c r="K13" s="11">
         <f>'QTR P&amp;L'!AH13+'QTR P&amp;L'!AI13+'QTR P&amp;L'!AJ13+'QTR P&amp;L'!AK13</f>
         <v/>
       </c>
+      <c r="L13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -14374,32 +14349,32 @@
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>FY2025E</t>
+          <t>FY2026E</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>FY2026E</t>
+          <t>FY2027E</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>FY2027E</t>
+          <t>FY2028E</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>FY2028E</t>
+          <t>FY2029E</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>FY2029E</t>
+          <t>FY2030E</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>FY2030E</t>
+          <t>FY2031E</t>
         </is>
       </c>
     </row>
@@ -14421,30 +14396,27 @@
       <c r="E2" s="4" t="n">
         <v>9556</v>
       </c>
-      <c r="F2" s="5">
-        <f>'QTR BS'!N2</f>
-        <v/>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2" s="11">
         <f>'QTR BS'!R2</f>
         <v/>
       </c>
-      <c r="H2" s="5">
+      <c r="G2" s="11">
         <f>'QTR BS'!V2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="H2" s="11">
         <f>'QTR BS'!Z2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="I2" s="11">
         <f>'QTR BS'!AD2</f>
         <v/>
       </c>
-      <c r="K2" s="5">
+      <c r="J2" s="11">
         <f>'QTR BS'!AH2</f>
         <v/>
       </c>
+      <c r="K2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -14464,30 +14436,27 @@
       <c r="E3" s="4" t="n">
         <v>6185</v>
       </c>
-      <c r="F3" s="5">
-        <f>'QTR BS'!N3</f>
-        <v/>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3" s="11">
         <f>'QTR BS'!R3</f>
         <v/>
       </c>
-      <c r="H3" s="5">
+      <c r="G3" s="11">
         <f>'QTR BS'!V3</f>
         <v/>
       </c>
-      <c r="I3" s="5">
+      <c r="H3" s="11">
         <f>'QTR BS'!Z3</f>
         <v/>
       </c>
-      <c r="J3" s="5">
+      <c r="I3" s="11">
         <f>'QTR BS'!AD3</f>
         <v/>
       </c>
-      <c r="K3" s="5">
+      <c r="J3" s="11">
         <f>'QTR BS'!AH3</f>
         <v/>
       </c>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -14507,30 +14476,27 @@
       <c r="E4" s="4" t="n">
         <v>7551</v>
       </c>
-      <c r="F4" s="5">
-        <f>'QTR BS'!N4</f>
-        <v/>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4" s="11">
         <f>'QTR BS'!R4</f>
         <v/>
       </c>
-      <c r="H4" s="5">
+      <c r="G4" s="11">
         <f>'QTR BS'!V4</f>
         <v/>
       </c>
-      <c r="I4" s="5">
+      <c r="H4" s="11">
         <f>'QTR BS'!Z4</f>
         <v/>
       </c>
-      <c r="J4" s="5">
+      <c r="I4" s="11">
         <f>'QTR BS'!AD4</f>
         <v/>
       </c>
-      <c r="K4" s="5">
+      <c r="J4" s="11">
         <f>'QTR BS'!AH4</f>
         <v/>
       </c>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -14550,30 +14516,27 @@
       <c r="E5" s="4" t="n">
         <v>2100</v>
       </c>
-      <c r="F5" s="5">
-        <f>'QTR BS'!N5</f>
-        <v/>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5" s="11">
         <f>'QTR BS'!R5</f>
         <v/>
       </c>
-      <c r="H5" s="5">
+      <c r="G5" s="11">
         <f>'QTR BS'!V5</f>
         <v/>
       </c>
-      <c r="I5" s="5">
+      <c r="H5" s="11">
         <f>'QTR BS'!Z5</f>
         <v/>
       </c>
-      <c r="J5" s="5">
+      <c r="I5" s="11">
         <f>'QTR BS'!AD5</f>
         <v/>
       </c>
-      <c r="K5" s="5">
+      <c r="J5" s="11">
         <f>'QTR BS'!AH5</f>
         <v/>
       </c>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -14640,30 +14603,27 @@
       <c r="E7" s="4" t="n">
         <v>23897</v>
       </c>
-      <c r="F7" s="5">
-        <f>'QTR BS'!N7</f>
-        <v/>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7" s="11">
         <f>'QTR BS'!R7</f>
         <v/>
       </c>
-      <c r="H7" s="5">
+      <c r="G7" s="11">
         <f>'QTR BS'!V7</f>
         <v/>
       </c>
-      <c r="I7" s="5">
+      <c r="H7" s="11">
         <f>'QTR BS'!Z7</f>
         <v/>
       </c>
-      <c r="J7" s="5">
+      <c r="I7" s="11">
         <f>'QTR BS'!AD7</f>
         <v/>
       </c>
-      <c r="K7" s="5">
+      <c r="J7" s="11">
         <f>'QTR BS'!AH7</f>
         <v/>
       </c>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -14683,30 +14643,27 @@
       <c r="E8" s="4" t="n">
         <v>41650</v>
       </c>
-      <c r="F8" s="5">
-        <f>'QTR BS'!N8</f>
-        <v/>
-      </c>
-      <c r="G8" s="5">
+      <c r="F8" s="11">
         <f>'QTR BS'!R8</f>
         <v/>
       </c>
-      <c r="H8" s="5">
+      <c r="G8" s="11">
         <f>'QTR BS'!V8</f>
         <v/>
       </c>
-      <c r="I8" s="5">
+      <c r="H8" s="11">
         <f>'QTR BS'!Z8</f>
         <v/>
       </c>
-      <c r="J8" s="5">
+      <c r="I8" s="11">
         <f>'QTR BS'!AD8</f>
         <v/>
       </c>
-      <c r="K8" s="5">
+      <c r="J8" s="11">
         <f>'QTR BS'!AH8</f>
         <v/>
       </c>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -14726,30 +14683,27 @@
       <c r="E9" s="4" t="n">
         <v>21910</v>
       </c>
-      <c r="F9" s="5">
-        <f>'QTR BS'!N9</f>
-        <v/>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="11">
         <f>'QTR BS'!R9</f>
         <v/>
       </c>
-      <c r="H9" s="5">
+      <c r="G9" s="11">
         <f>'QTR BS'!V9</f>
         <v/>
       </c>
-      <c r="I9" s="5">
+      <c r="H9" s="11">
         <f>'QTR BS'!Z9</f>
         <v/>
       </c>
-      <c r="J9" s="5">
+      <c r="I9" s="11">
         <f>'QTR BS'!AD9</f>
         <v/>
       </c>
-      <c r="K9" s="5">
+      <c r="J9" s="11">
         <f>'QTR BS'!AH9</f>
         <v/>
       </c>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -14769,30 +14723,27 @@
       <c r="E10" s="4" t="n">
         <v>12381</v>
       </c>
-      <c r="F10" s="5">
-        <f>'QTR BS'!N10</f>
-        <v/>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="11">
         <f>'QTR BS'!R10</f>
         <v/>
       </c>
-      <c r="H10" s="5">
+      <c r="G10" s="11">
         <f>'QTR BS'!V10</f>
         <v/>
       </c>
-      <c r="I10" s="5">
+      <c r="H10" s="11">
         <f>'QTR BS'!Z10</f>
         <v/>
       </c>
-      <c r="J10" s="5">
+      <c r="I10" s="11">
         <f>'QTR BS'!AD10</f>
         <v/>
       </c>
-      <c r="K10" s="5">
+      <c r="J10" s="11">
         <f>'QTR BS'!AH10</f>
         <v/>
       </c>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -14859,30 +14810,27 @@
       <c r="E12" s="4" t="n">
         <v>15227</v>
       </c>
-      <c r="F12" s="5">
-        <f>'QTR BS'!N12</f>
-        <v/>
-      </c>
-      <c r="G12" s="5">
+      <c r="F12" s="11">
         <f>'QTR BS'!R12</f>
         <v/>
       </c>
-      <c r="H12" s="5">
+      <c r="G12" s="11">
         <f>'QTR BS'!V12</f>
         <v/>
       </c>
-      <c r="I12" s="5">
+      <c r="H12" s="11">
         <f>'QTR BS'!Z12</f>
         <v/>
       </c>
-      <c r="J12" s="5">
+      <c r="I12" s="11">
         <f>'QTR BS'!AD12</f>
         <v/>
       </c>
-      <c r="K12" s="5">
+      <c r="J12" s="11">
         <f>'QTR BS'!AH12</f>
         <v/>
       </c>
+      <c r="K12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -14902,30 +14850,27 @@
       <c r="E13" s="4" t="n">
         <v>11318</v>
       </c>
-      <c r="F13" s="5">
-        <f>'QTR BS'!N13</f>
-        <v/>
-      </c>
-      <c r="G13" s="5">
+      <c r="F13" s="11">
         <f>'QTR BS'!R13</f>
         <v/>
       </c>
-      <c r="H13" s="5">
+      <c r="G13" s="11">
         <f>'QTR BS'!V13</f>
         <v/>
       </c>
-      <c r="I13" s="5">
+      <c r="H13" s="11">
         <f>'QTR BS'!Z13</f>
         <v/>
       </c>
-      <c r="J13" s="5">
+      <c r="I13" s="11">
         <f>'QTR BS'!AD13</f>
         <v/>
       </c>
-      <c r="K13" s="5">
+      <c r="J13" s="11">
         <f>'QTR BS'!AH13</f>
         <v/>
       </c>
+      <c r="K13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -14945,30 +14890,27 @@
       <c r="E14" s="4" t="n">
         <v>9513</v>
       </c>
-      <c r="F14" s="5">
-        <f>'QTR BS'!N14</f>
-        <v/>
-      </c>
-      <c r="G14" s="5">
+      <c r="F14" s="11">
         <f>'QTR BS'!R14</f>
         <v/>
       </c>
-      <c r="H14" s="5">
+      <c r="G14" s="11">
         <f>'QTR BS'!V14</f>
         <v/>
       </c>
-      <c r="I14" s="5">
+      <c r="H14" s="11">
         <f>'QTR BS'!Z14</f>
         <v/>
       </c>
-      <c r="J14" s="5">
+      <c r="I14" s="11">
         <f>'QTR BS'!AD14</f>
         <v/>
       </c>
-      <c r="K14" s="5">
+      <c r="J14" s="11">
         <f>'QTR BS'!AH14</f>
         <v/>
       </c>
+      <c r="K14" s="5" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -15035,30 +14977,27 @@
       <c r="E16" s="4" t="n">
         <v>24995</v>
       </c>
-      <c r="F16" s="5">
-        <f>'QTR BS'!N16</f>
-        <v/>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16" s="11">
         <f>'QTR BS'!R16</f>
         <v/>
       </c>
-      <c r="H16" s="5">
+      <c r="G16" s="11">
         <f>'QTR BS'!V16</f>
         <v/>
       </c>
-      <c r="I16" s="5">
+      <c r="H16" s="11">
         <f>'QTR BS'!Z16</f>
         <v/>
       </c>
-      <c r="J16" s="5">
+      <c r="I16" s="11">
         <f>'QTR BS'!AD16</f>
         <v/>
       </c>
-      <c r="K16" s="5">
+      <c r="J16" s="11">
         <f>'QTR BS'!AH16</f>
         <v/>
       </c>
+      <c r="K16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -15078,30 +15017,27 @@
       <c r="E17" s="4" t="n">
         <v>5774</v>
       </c>
-      <c r="F17" s="5">
-        <f>'QTR BS'!N17</f>
-        <v/>
-      </c>
-      <c r="G17" s="5">
+      <c r="F17" s="11">
         <f>'QTR BS'!R17</f>
         <v/>
       </c>
-      <c r="H17" s="5">
+      <c r="G17" s="11">
         <f>'QTR BS'!V17</f>
         <v/>
       </c>
-      <c r="I17" s="5">
+      <c r="H17" s="11">
         <f>'QTR BS'!Z17</f>
         <v/>
       </c>
-      <c r="J17" s="5">
+      <c r="I17" s="11">
         <f>'QTR BS'!AD17</f>
         <v/>
       </c>
-      <c r="K17" s="5">
+      <c r="J17" s="11">
         <f>'QTR BS'!AH17</f>
         <v/>
       </c>
+      <c r="K17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -15121,30 +15057,27 @@
       <c r="E18" s="4" t="n">
         <v>6120</v>
       </c>
-      <c r="F18" s="5">
-        <f>'QTR BS'!N18</f>
-        <v/>
-      </c>
-      <c r="G18" s="5">
+      <c r="F18" s="11">
         <f>'QTR BS'!R18</f>
         <v/>
       </c>
-      <c r="H18" s="5">
+      <c r="G18" s="11">
         <f>'QTR BS'!V18</f>
         <v/>
       </c>
-      <c r="I18" s="5">
+      <c r="H18" s="11">
         <f>'QTR BS'!Z18</f>
         <v/>
       </c>
-      <c r="J18" s="5">
+      <c r="I18" s="11">
         <f>'QTR BS'!AD18</f>
         <v/>
       </c>
-      <c r="K18" s="5">
+      <c r="J18" s="11">
         <f>'QTR BS'!AH18</f>
         <v/>
       </c>
+      <c r="K18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -15211,30 +15144,27 @@
       <c r="E20" s="4" t="n">
         <v>777</v>
       </c>
-      <c r="F20" s="5">
-        <f>'QTR BS'!N20</f>
-        <v/>
-      </c>
-      <c r="G20" s="5">
+      <c r="F20" s="11">
         <f>'QTR BS'!R20</f>
         <v/>
       </c>
-      <c r="H20" s="5">
+      <c r="G20" s="11">
         <f>'QTR BS'!V20</f>
         <v/>
       </c>
-      <c r="I20" s="5">
+      <c r="H20" s="11">
         <f>'QTR BS'!Z20</f>
         <v/>
       </c>
-      <c r="J20" s="5">
+      <c r="I20" s="11">
         <f>'QTR BS'!AD20</f>
         <v/>
       </c>
-      <c r="K20" s="5">
+      <c r="J20" s="11">
         <f>'QTR BS'!AH20</f>
         <v/>
       </c>
+      <c r="K20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -15254,30 +15184,27 @@
       <c r="E21" s="4" t="n">
         <v>4009</v>
       </c>
-      <c r="F21" s="5">
-        <f>'QTR BS'!N21</f>
-        <v/>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="11">
         <f>'QTR BS'!R21</f>
         <v/>
       </c>
-      <c r="H21" s="5">
+      <c r="G21" s="11">
         <f>'QTR BS'!V21</f>
         <v/>
       </c>
-      <c r="I21" s="5">
+      <c r="H21" s="11">
         <f>'QTR BS'!Z21</f>
         <v/>
       </c>
-      <c r="J21" s="5">
+      <c r="I21" s="11">
         <f>'QTR BS'!AD21</f>
         <v/>
       </c>
-      <c r="K21" s="5">
+      <c r="J21" s="11">
         <f>'QTR BS'!AH21</f>
         <v/>
       </c>
+      <c r="K21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -15297,30 +15224,27 @@
       <c r="E22" s="4" t="n">
         <v>68770</v>
       </c>
-      <c r="F22" s="5">
-        <f>'QTR BS'!N22</f>
-        <v/>
-      </c>
-      <c r="G22" s="5">
+      <c r="F22" s="11">
         <f>'QTR BS'!R22</f>
         <v/>
       </c>
-      <c r="H22" s="5">
+      <c r="G22" s="11">
         <f>'QTR BS'!V22</f>
         <v/>
       </c>
-      <c r="I22" s="5">
+      <c r="H22" s="11">
         <f>'QTR BS'!Z22</f>
         <v/>
       </c>
-      <c r="J22" s="5">
+      <c r="I22" s="11">
         <f>'QTR BS'!AD22</f>
         <v/>
       </c>
-      <c r="K22" s="5">
+      <c r="J22" s="11">
         <f>'QTR BS'!AH22</f>
         <v/>
       </c>
+      <c r="K22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -15340,30 +15264,27 @@
       <c r="E23" s="4" t="n">
         <v>-672</v>
       </c>
-      <c r="F23" s="5">
-        <f>'QTR BS'!N23</f>
-        <v/>
-      </c>
-      <c r="G23" s="5">
+      <c r="F23" s="11">
         <f>'QTR BS'!R23</f>
         <v/>
       </c>
-      <c r="H23" s="5">
+      <c r="G23" s="11">
         <f>'QTR BS'!V23</f>
         <v/>
       </c>
-      <c r="I23" s="5">
+      <c r="H23" s="11">
         <f>'QTR BS'!Z23</f>
         <v/>
       </c>
-      <c r="J23" s="5">
+      <c r="I23" s="11">
         <f>'QTR BS'!AD23</f>
         <v/>
       </c>
-      <c r="K23" s="5">
+      <c r="J23" s="11">
         <f>'QTR BS'!AH23</f>
         <v/>
       </c>
+      <c r="K23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -15383,30 +15304,27 @@
       <c r="E24" s="4" t="n">
         <v>-12143</v>
       </c>
-      <c r="F24" s="5">
-        <f>'QTR BS'!N24</f>
-        <v/>
-      </c>
-      <c r="G24" s="5">
+      <c r="F24" s="11">
         <f>'QTR BS'!R24</f>
         <v/>
       </c>
-      <c r="H24" s="5">
+      <c r="G24" s="11">
         <f>'QTR BS'!V24</f>
         <v/>
       </c>
-      <c r="I24" s="5">
+      <c r="H24" s="11">
         <f>'QTR BS'!Z24</f>
         <v/>
       </c>
-      <c r="J24" s="5">
+      <c r="I24" s="11">
         <f>'QTR BS'!AD24</f>
         <v/>
       </c>
-      <c r="K24" s="5">
+      <c r="J24" s="11">
         <f>'QTR BS'!AH24</f>
         <v/>
       </c>
+      <c r="K24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -15426,30 +15344,27 @@
       <c r="E25" s="4" t="n">
         <v>-138702</v>
       </c>
-      <c r="F25" s="5">
-        <f>'QTR BS'!N25</f>
-        <v/>
-      </c>
-      <c r="G25" s="5">
+      <c r="F25" s="11">
         <f>'QTR BS'!R25</f>
         <v/>
       </c>
-      <c r="H25" s="5">
+      <c r="G25" s="11">
         <f>'QTR BS'!V25</f>
         <v/>
       </c>
-      <c r="I25" s="5">
+      <c r="H25" s="11">
         <f>'QTR BS'!Z25</f>
         <v/>
       </c>
-      <c r="J25" s="5">
+      <c r="I25" s="11">
         <f>'QTR BS'!AD25</f>
         <v/>
       </c>
-      <c r="K25" s="5">
+      <c r="J25" s="11">
         <f>'QTR BS'!AH25</f>
         <v/>
       </c>
+      <c r="K25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -15469,30 +15384,27 @@
       <c r="E26" s="4" t="n">
         <v>129973</v>
       </c>
-      <c r="F26" s="5">
-        <f>'QTR BS'!N26</f>
-        <v/>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="11">
         <f>'QTR BS'!R26</f>
         <v/>
       </c>
-      <c r="H26" s="5">
+      <c r="G26" s="11">
         <f>'QTR BS'!V26</f>
         <v/>
       </c>
-      <c r="I26" s="5">
+      <c r="H26" s="11">
         <f>'QTR BS'!Z26</f>
         <v/>
       </c>
-      <c r="J26" s="5">
+      <c r="I26" s="11">
         <f>'QTR BS'!AD26</f>
         <v/>
       </c>
-      <c r="K26" s="5">
+      <c r="J26" s="11">
         <f>'QTR BS'!AH26</f>
         <v/>
       </c>
+      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -15512,30 +15424,27 @@
       <c r="E27" s="4" t="n">
         <v>272</v>
       </c>
-      <c r="F27" s="5">
-        <f>'QTR BS'!N27</f>
-        <v/>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="11">
         <f>'QTR BS'!R27</f>
         <v/>
       </c>
-      <c r="H27" s="5">
+      <c r="G27" s="11">
         <f>'QTR BS'!V27</f>
         <v/>
       </c>
-      <c r="I27" s="5">
+      <c r="H27" s="11">
         <f>'QTR BS'!Z27</f>
         <v/>
       </c>
-      <c r="J27" s="5">
+      <c r="I27" s="11">
         <f>'QTR BS'!AD27</f>
         <v/>
       </c>
-      <c r="K27" s="5">
+      <c r="J27" s="11">
         <f>'QTR BS'!AH27</f>
         <v/>
       </c>
+      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -15688,32 +15597,32 @@
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>FY2025E</t>
+          <t>FY2026E</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>FY2026E</t>
+          <t>FY2027E</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>FY2027E</t>
+          <t>FY2028E</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>FY2028E</t>
+          <t>FY2029E</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>FY2029E</t>
+          <t>FY2030E</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>FY2030E</t>
+          <t>FY2031E</t>
         </is>
       </c>
     </row>
@@ -15738,30 +15647,27 @@
       <c r="F2" s="4" t="n">
         <v>16065</v>
       </c>
-      <c r="G2" s="5">
-        <f>'QTR CF'!N2+'QTR CF'!O2+'QTR CF'!P2+'QTR CF'!Q2</f>
-        <v/>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2" s="11">
         <f>'QTR CF'!R2+'QTR CF'!S2+'QTR CF'!T2+'QTR CF'!U2</f>
         <v/>
       </c>
-      <c r="I2" s="5">
+      <c r="H2" s="11">
         <f>'QTR CF'!V2+'QTR CF'!W2+'QTR CF'!X2+'QTR CF'!Y2</f>
         <v/>
       </c>
-      <c r="J2" s="5">
+      <c r="I2" s="11">
         <f>'QTR CF'!Z2+'QTR CF'!AA2+'QTR CF'!AB2+'QTR CF'!AC2</f>
         <v/>
       </c>
-      <c r="K2" s="5">
+      <c r="J2" s="11">
         <f>'QTR CF'!AD2+'QTR CF'!AE2+'QTR CF'!AF2+'QTR CF'!AG2</f>
         <v/>
       </c>
-      <c r="L2" s="5">
+      <c r="K2" s="11">
         <f>'QTR CF'!AH2+'QTR CF'!AI2+'QTR CF'!AJ2+'QTR CF'!AK2</f>
         <v/>
       </c>
+      <c r="L2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -15784,30 +15690,27 @@
       <c r="F3" s="4" t="n">
         <v>2847</v>
       </c>
-      <c r="G3" s="5">
-        <f>'QTR CF'!N3+'QTR CF'!O3+'QTR CF'!P3+'QTR CF'!Q3</f>
-        <v/>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="11">
         <f>'QTR CF'!R3+'QTR CF'!S3+'QTR CF'!T3+'QTR CF'!U3</f>
         <v/>
       </c>
-      <c r="I3" s="5">
+      <c r="H3" s="11">
         <f>'QTR CF'!V3+'QTR CF'!W3+'QTR CF'!X3+'QTR CF'!Y3</f>
         <v/>
       </c>
-      <c r="J3" s="5">
+      <c r="I3" s="11">
         <f>'QTR CF'!Z3+'QTR CF'!AA3+'QTR CF'!AB3+'QTR CF'!AC3</f>
         <v/>
       </c>
-      <c r="K3" s="5">
+      <c r="J3" s="11">
         <f>'QTR CF'!AD3+'QTR CF'!AE3+'QTR CF'!AF3+'QTR CF'!AG3</f>
         <v/>
       </c>
-      <c r="L3" s="5">
+      <c r="K3" s="11">
         <f>'QTR CF'!AH3+'QTR CF'!AI3+'QTR CF'!AJ3+'QTR CF'!AK3</f>
         <v/>
       </c>
+      <c r="L3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -15858,30 +15761,27 @@
       <c r="F5" s="4" t="n">
         <v>476</v>
       </c>
-      <c r="G5" s="5">
-        <f>'QTR CF'!N4+'QTR CF'!O4+'QTR CF'!P4+'QTR CF'!Q4</f>
-        <v/>
-      </c>
-      <c r="H5" s="5">
+      <c r="G5" s="11">
         <f>'QTR CF'!R4+'QTR CF'!S4+'QTR CF'!T4+'QTR CF'!U4</f>
         <v/>
       </c>
-      <c r="I5" s="5">
+      <c r="H5" s="11">
         <f>'QTR CF'!V4+'QTR CF'!W4+'QTR CF'!X4+'QTR CF'!Y4</f>
         <v/>
       </c>
-      <c r="J5" s="5">
+      <c r="I5" s="11">
         <f>'QTR CF'!Z4+'QTR CF'!AA4+'QTR CF'!AB4+'QTR CF'!AC4</f>
         <v/>
       </c>
-      <c r="K5" s="5">
+      <c r="J5" s="11">
         <f>'QTR CF'!AD4+'QTR CF'!AE4+'QTR CF'!AF4+'QTR CF'!AG4</f>
         <v/>
       </c>
-      <c r="L5" s="5">
+      <c r="K5" s="11">
         <f>'QTR CF'!AH4+'QTR CF'!AI4+'QTR CF'!AJ4+'QTR CF'!AK4</f>
         <v/>
       </c>
+      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -15904,30 +15804,27 @@
       <c r="F6" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="G6" s="5">
-        <f>'QTR CF'!N5+'QTR CF'!O5+'QTR CF'!P5+'QTR CF'!Q5</f>
-        <v/>
-      </c>
-      <c r="H6" s="5">
+      <c r="G6" s="11">
         <f>'QTR CF'!R5+'QTR CF'!S5+'QTR CF'!T5+'QTR CF'!U5</f>
         <v/>
       </c>
-      <c r="I6" s="5">
+      <c r="H6" s="11">
         <f>'QTR CF'!V5+'QTR CF'!W5+'QTR CF'!X5+'QTR CF'!Y5</f>
         <v/>
       </c>
-      <c r="J6" s="5">
+      <c r="I6" s="11">
         <f>'QTR CF'!Z5+'QTR CF'!AA5+'QTR CF'!AB5+'QTR CF'!AC5</f>
         <v/>
       </c>
-      <c r="K6" s="5">
+      <c r="J6" s="11">
         <f>'QTR CF'!AD5+'QTR CF'!AE5+'QTR CF'!AF5+'QTR CF'!AG5</f>
         <v/>
       </c>
-      <c r="L6" s="5">
+      <c r="K6" s="11">
         <f>'QTR CF'!AH5+'QTR CF'!AI5+'QTR CF'!AJ5+'QTR CF'!AK5</f>
         <v/>
       </c>
+      <c r="L6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -15950,30 +15847,27 @@
       <c r="F7" s="4" t="n">
         <v>755</v>
       </c>
-      <c r="G7" s="5">
-        <f>'QTR CF'!N6+'QTR CF'!O6+'QTR CF'!P6+'QTR CF'!Q6</f>
-        <v/>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7" s="11">
         <f>'QTR CF'!R6+'QTR CF'!S6+'QTR CF'!T6+'QTR CF'!U6</f>
         <v/>
       </c>
-      <c r="I7" s="5">
+      <c r="H7" s="11">
         <f>'QTR CF'!V6+'QTR CF'!W6+'QTR CF'!X6+'QTR CF'!Y6</f>
         <v/>
       </c>
-      <c r="J7" s="5">
+      <c r="I7" s="11">
         <f>'QTR CF'!Z6+'QTR CF'!AA6+'QTR CF'!AB6+'QTR CF'!AC6</f>
         <v/>
       </c>
-      <c r="K7" s="5">
+      <c r="J7" s="11">
         <f>'QTR CF'!AD6+'QTR CF'!AE6+'QTR CF'!AF6+'QTR CF'!AG6</f>
         <v/>
       </c>
-      <c r="L7" s="5">
+      <c r="K7" s="11">
         <f>'QTR CF'!AH6+'QTR CF'!AI6+'QTR CF'!AJ6+'QTR CF'!AK6</f>
         <v/>
       </c>
+      <c r="L7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -15996,30 +15890,27 @@
       <c r="F8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="5">
-        <f>'QTR CF'!N7+'QTR CF'!O7+'QTR CF'!P7+'QTR CF'!Q7</f>
-        <v/>
-      </c>
-      <c r="H8" s="5">
+      <c r="G8" s="11">
         <f>'QTR CF'!R7+'QTR CF'!S7+'QTR CF'!T7+'QTR CF'!U7</f>
         <v/>
       </c>
-      <c r="I8" s="5">
+      <c r="H8" s="11">
         <f>'QTR CF'!V7+'QTR CF'!W7+'QTR CF'!X7+'QTR CF'!Y7</f>
         <v/>
       </c>
-      <c r="J8" s="5">
+      <c r="I8" s="11">
         <f>'QTR CF'!Z7+'QTR CF'!AA7+'QTR CF'!AB7+'QTR CF'!AC7</f>
         <v/>
       </c>
-      <c r="K8" s="5">
+      <c r="J8" s="11">
         <f>'QTR CF'!AD7+'QTR CF'!AE7+'QTR CF'!AF7+'QTR CF'!AG7</f>
         <v/>
       </c>
-      <c r="L8" s="5">
+      <c r="K8" s="11">
         <f>'QTR CF'!AH7+'QTR CF'!AI7+'QTR CF'!AJ7+'QTR CF'!AK7</f>
         <v/>
       </c>
+      <c r="L8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -16042,30 +15933,27 @@
       <c r="F9" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="G9" s="5">
-        <f>'QTR CF'!N8+'QTR CF'!O8+'QTR CF'!P8+'QTR CF'!Q8</f>
-        <v/>
-      </c>
-      <c r="H9" s="5">
+      <c r="G9" s="11">
         <f>'QTR CF'!R8+'QTR CF'!S8+'QTR CF'!T8+'QTR CF'!U8</f>
         <v/>
       </c>
-      <c r="I9" s="5">
+      <c r="H9" s="11">
         <f>'QTR CF'!V8+'QTR CF'!W8+'QTR CF'!X8+'QTR CF'!Y8</f>
         <v/>
       </c>
-      <c r="J9" s="5">
+      <c r="I9" s="11">
         <f>'QTR CF'!Z8+'QTR CF'!AA8+'QTR CF'!AB8+'QTR CF'!AC8</f>
         <v/>
       </c>
-      <c r="K9" s="5">
+      <c r="J9" s="11">
         <f>'QTR CF'!AD8+'QTR CF'!AE8+'QTR CF'!AF8+'QTR CF'!AG8</f>
         <v/>
       </c>
-      <c r="L9" s="5">
+      <c r="K9" s="11">
         <f>'QTR CF'!AH8+'QTR CF'!AI8+'QTR CF'!AJ8+'QTR CF'!AK8</f>
         <v/>
       </c>
+      <c r="L9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -16088,30 +15976,27 @@
       <c r="F10" s="4" t="n">
         <v>-324</v>
       </c>
-      <c r="G10" s="5">
-        <f>'QTR CF'!N9+'QTR CF'!O9+'QTR CF'!P9+'QTR CF'!Q9</f>
-        <v/>
-      </c>
-      <c r="H10" s="5">
+      <c r="G10" s="11">
         <f>'QTR CF'!R9+'QTR CF'!S9+'QTR CF'!T9+'QTR CF'!U9</f>
         <v/>
       </c>
-      <c r="I10" s="5">
+      <c r="H10" s="11">
         <f>'QTR CF'!V9+'QTR CF'!W9+'QTR CF'!X9+'QTR CF'!Y9</f>
         <v/>
       </c>
-      <c r="J10" s="5">
+      <c r="I10" s="11">
         <f>'QTR CF'!Z9+'QTR CF'!AA9+'QTR CF'!AB9+'QTR CF'!AC9</f>
         <v/>
       </c>
-      <c r="K10" s="5">
+      <c r="J10" s="11">
         <f>'QTR CF'!AD9+'QTR CF'!AE9+'QTR CF'!AF9+'QTR CF'!AG9</f>
         <v/>
       </c>
-      <c r="L10" s="5">
+      <c r="K10" s="11">
         <f>'QTR CF'!AH9+'QTR CF'!AI9+'QTR CF'!AJ9+'QTR CF'!AK9</f>
         <v/>
       </c>
+      <c r="L10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -16134,30 +16019,27 @@
       <c r="F11" s="4" t="n">
         <v>-542</v>
       </c>
-      <c r="G11" s="5">
-        <f>'QTR CF'!N10+'QTR CF'!O10+'QTR CF'!P10+'QTR CF'!Q10</f>
-        <v/>
-      </c>
-      <c r="H11" s="5">
+      <c r="G11" s="11">
         <f>'QTR CF'!R10+'QTR CF'!S10+'QTR CF'!T10+'QTR CF'!U10</f>
         <v/>
       </c>
-      <c r="I11" s="5">
+      <c r="H11" s="11">
         <f>'QTR CF'!V10+'QTR CF'!W10+'QTR CF'!X10+'QTR CF'!Y10</f>
         <v/>
       </c>
-      <c r="J11" s="5">
+      <c r="I11" s="11">
         <f>'QTR CF'!Z10+'QTR CF'!AA10+'QTR CF'!AB10+'QTR CF'!AC10</f>
         <v/>
       </c>
-      <c r="K11" s="5">
+      <c r="J11" s="11">
         <f>'QTR CF'!AD10+'QTR CF'!AE10+'QTR CF'!AF10+'QTR CF'!AG10</f>
         <v/>
       </c>
-      <c r="L11" s="5">
+      <c r="K11" s="11">
         <f>'QTR CF'!AH10+'QTR CF'!AI10+'QTR CF'!AJ10+'QTR CF'!AK10</f>
         <v/>
       </c>
+      <c r="L11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -16180,30 +16062,27 @@
       <c r="F12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G12" s="5">
-        <f>'QTR CF'!N11+'QTR CF'!O11+'QTR CF'!P11+'QTR CF'!Q11</f>
-        <v/>
-      </c>
-      <c r="H12" s="5">
+      <c r="G12" s="11">
         <f>'QTR CF'!R11+'QTR CF'!S11+'QTR CF'!T11+'QTR CF'!U11</f>
         <v/>
       </c>
-      <c r="I12" s="5">
+      <c r="H12" s="11">
         <f>'QTR CF'!V11+'QTR CF'!W11+'QTR CF'!X11+'QTR CF'!Y11</f>
         <v/>
       </c>
-      <c r="J12" s="5">
+      <c r="I12" s="11">
         <f>'QTR CF'!Z11+'QTR CF'!AA11+'QTR CF'!AB11+'QTR CF'!AC11</f>
         <v/>
       </c>
-      <c r="K12" s="5">
+      <c r="J12" s="11">
         <f>'QTR CF'!AD11+'QTR CF'!AE11+'QTR CF'!AF11+'QTR CF'!AG11</f>
         <v/>
       </c>
-      <c r="L12" s="5">
+      <c r="K12" s="11">
         <f>'QTR CF'!AH11+'QTR CF'!AI11+'QTR CF'!AJ11+'QTR CF'!AK11</f>
         <v/>
       </c>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -16226,30 +16105,27 @@
       <c r="F13" s="4" t="n">
         <v>-1653</v>
       </c>
-      <c r="G13" s="5">
-        <f>'QTR CF'!N12+'QTR CF'!O12+'QTR CF'!P12+'QTR CF'!Q12</f>
-        <v/>
-      </c>
-      <c r="H13" s="5">
+      <c r="G13" s="11">
         <f>'QTR CF'!R12+'QTR CF'!S12+'QTR CF'!T12+'QTR CF'!U12</f>
         <v/>
       </c>
-      <c r="I13" s="5">
+      <c r="H13" s="11">
         <f>'QTR CF'!V12+'QTR CF'!W12+'QTR CF'!X12+'QTR CF'!Y12</f>
         <v/>
       </c>
-      <c r="J13" s="5">
+      <c r="I13" s="11">
         <f>'QTR CF'!Z12+'QTR CF'!AA12+'QTR CF'!AB12+'QTR CF'!AC12</f>
         <v/>
       </c>
-      <c r="K13" s="5">
+      <c r="J13" s="11">
         <f>'QTR CF'!AD12+'QTR CF'!AE12+'QTR CF'!AF12+'QTR CF'!AG12</f>
         <v/>
       </c>
-      <c r="L13" s="5">
+      <c r="K13" s="11">
         <f>'QTR CF'!AH12+'QTR CF'!AI12+'QTR CF'!AJ12+'QTR CF'!AK12</f>
         <v/>
       </c>
+      <c r="L13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -16323,30 +16199,27 @@
       <c r="F15" s="4" t="n">
         <v>-3773</v>
       </c>
-      <c r="G15" s="5">
-        <f>'QTR CF'!N14+'QTR CF'!O14+'QTR CF'!P14+'QTR CF'!Q14</f>
-        <v/>
-      </c>
-      <c r="H15" s="5">
+      <c r="G15" s="11">
         <f>'QTR CF'!R14+'QTR CF'!S14+'QTR CF'!T14+'QTR CF'!U14</f>
         <v/>
       </c>
-      <c r="I15" s="5">
+      <c r="H15" s="11">
         <f>'QTR CF'!V14+'QTR CF'!W14+'QTR CF'!X14+'QTR CF'!Y14</f>
         <v/>
       </c>
-      <c r="J15" s="5">
+      <c r="I15" s="11">
         <f>'QTR CF'!Z14+'QTR CF'!AA14+'QTR CF'!AB14+'QTR CF'!AC14</f>
         <v/>
       </c>
-      <c r="K15" s="5">
+      <c r="J15" s="11">
         <f>'QTR CF'!AD14+'QTR CF'!AE14+'QTR CF'!AF14+'QTR CF'!AG14</f>
         <v/>
       </c>
-      <c r="L15" s="5">
+      <c r="K15" s="11">
         <f>'QTR CF'!AH14+'QTR CF'!AI14+'QTR CF'!AJ14+'QTR CF'!AK14</f>
         <v/>
       </c>
+      <c r="L15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -16369,30 +16242,27 @@
       <c r="F16" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="G16" s="5">
-        <f>'QTR CF'!N15+'QTR CF'!O15+'QTR CF'!P15+'QTR CF'!Q15</f>
-        <v/>
-      </c>
-      <c r="H16" s="5">
+      <c r="G16" s="11">
         <f>'QTR CF'!R15+'QTR CF'!S15+'QTR CF'!T15+'QTR CF'!U15</f>
         <v/>
       </c>
-      <c r="I16" s="5">
+      <c r="H16" s="11">
         <f>'QTR CF'!V15+'QTR CF'!W15+'QTR CF'!X15+'QTR CF'!Y15</f>
         <v/>
       </c>
-      <c r="J16" s="5">
+      <c r="I16" s="11">
         <f>'QTR CF'!Z15+'QTR CF'!AA15+'QTR CF'!AB15+'QTR CF'!AC15</f>
         <v/>
       </c>
-      <c r="K16" s="5">
+      <c r="J16" s="11">
         <f>'QTR CF'!AD15+'QTR CF'!AE15+'QTR CF'!AF15+'QTR CF'!AG15</f>
         <v/>
       </c>
-      <c r="L16" s="5">
+      <c r="K16" s="11">
         <f>'QTR CF'!AH15+'QTR CF'!AI15+'QTR CF'!AJ15+'QTR CF'!AK15</f>
         <v/>
       </c>
+      <c r="L16" s="5" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -16415,30 +16285,27 @@
       <c r="F17" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="G17" s="5">
-        <f>'QTR CF'!N16+'QTR CF'!O16+'QTR CF'!P16+'QTR CF'!Q16</f>
-        <v/>
-      </c>
-      <c r="H17" s="5">
+      <c r="G17" s="11">
         <f>'QTR CF'!R16+'QTR CF'!S16+'QTR CF'!T16+'QTR CF'!U16</f>
         <v/>
       </c>
-      <c r="I17" s="5">
+      <c r="H17" s="11">
         <f>'QTR CF'!V16+'QTR CF'!W16+'QTR CF'!X16+'QTR CF'!Y16</f>
         <v/>
       </c>
-      <c r="J17" s="5">
+      <c r="I17" s="11">
         <f>'QTR CF'!Z16+'QTR CF'!AA16+'QTR CF'!AB16+'QTR CF'!AC16</f>
         <v/>
       </c>
-      <c r="K17" s="5">
+      <c r="J17" s="11">
         <f>'QTR CF'!AD16+'QTR CF'!AE16+'QTR CF'!AF16+'QTR CF'!AG16</f>
         <v/>
       </c>
-      <c r="L17" s="5">
+      <c r="K17" s="11">
         <f>'QTR CF'!AH16+'QTR CF'!AI16+'QTR CF'!AJ16+'QTR CF'!AK16</f>
         <v/>
       </c>
+      <c r="L17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -16461,30 +16328,27 @@
       <c r="F18" s="4" t="n">
         <v>-141</v>
       </c>
-      <c r="G18" s="5">
-        <f>'QTR CF'!N18+'QTR CF'!O18+'QTR CF'!P18+'QTR CF'!Q18</f>
-        <v/>
-      </c>
-      <c r="H18" s="5">
+      <c r="G18" s="11">
         <f>'QTR CF'!R18+'QTR CF'!S18+'QTR CF'!T18+'QTR CF'!U18</f>
         <v/>
       </c>
-      <c r="I18" s="5">
+      <c r="H18" s="11">
         <f>'QTR CF'!V18+'QTR CF'!W18+'QTR CF'!X18+'QTR CF'!Y18</f>
         <v/>
       </c>
-      <c r="J18" s="5">
+      <c r="I18" s="11">
         <f>'QTR CF'!Z18+'QTR CF'!AA18+'QTR CF'!AB18+'QTR CF'!AC18</f>
         <v/>
       </c>
-      <c r="K18" s="5">
+      <c r="J18" s="11">
         <f>'QTR CF'!AD18+'QTR CF'!AE18+'QTR CF'!AF18+'QTR CF'!AG18</f>
         <v/>
       </c>
-      <c r="L18" s="5">
+      <c r="K18" s="11">
         <f>'QTR CF'!AH18+'QTR CF'!AI18+'QTR CF'!AJ18+'QTR CF'!AK18</f>
         <v/>
       </c>
+      <c r="L18" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -16558,30 +16422,27 @@
       <c r="F20" s="4" t="n">
         <v>-9872</v>
       </c>
-      <c r="G20" s="5">
-        <f>'QTR CF'!N20+'QTR CF'!O20+'QTR CF'!P20+'QTR CF'!Q20</f>
-        <v/>
-      </c>
-      <c r="H20" s="5">
+      <c r="G20" s="11">
         <f>'QTR CF'!R20+'QTR CF'!S20+'QTR CF'!T20+'QTR CF'!U20</f>
         <v/>
       </c>
-      <c r="I20" s="5">
+      <c r="H20" s="11">
         <f>'QTR CF'!V20+'QTR CF'!W20+'QTR CF'!X20+'QTR CF'!Y20</f>
         <v/>
       </c>
-      <c r="J20" s="5">
+      <c r="I20" s="11">
         <f>'QTR CF'!Z20+'QTR CF'!AA20+'QTR CF'!AB20+'QTR CF'!AC20</f>
         <v/>
       </c>
-      <c r="K20" s="5">
+      <c r="J20" s="11">
         <f>'QTR CF'!AD20+'QTR CF'!AE20+'QTR CF'!AF20+'QTR CF'!AG20</f>
         <v/>
       </c>
-      <c r="L20" s="5">
+      <c r="K20" s="11">
         <f>'QTR CF'!AH20+'QTR CF'!AI20+'QTR CF'!AJ20+'QTR CF'!AK20</f>
         <v/>
       </c>
+      <c r="L20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -16604,30 +16465,27 @@
       <c r="F21" s="4" t="n">
         <v>8020</v>
       </c>
-      <c r="G21" s="5">
-        <f>'QTR CF'!N21+'QTR CF'!O21+'QTR CF'!P21+'QTR CF'!Q21</f>
-        <v/>
-      </c>
-      <c r="H21" s="5">
+      <c r="G21" s="11">
         <f>'QTR CF'!R21+'QTR CF'!S21+'QTR CF'!T21+'QTR CF'!U21</f>
         <v/>
       </c>
-      <c r="I21" s="5">
+      <c r="H21" s="11">
         <f>'QTR CF'!V21+'QTR CF'!W21+'QTR CF'!X21+'QTR CF'!Y21</f>
         <v/>
       </c>
-      <c r="J21" s="5">
+      <c r="I21" s="11">
         <f>'QTR CF'!Z21+'QTR CF'!AA21+'QTR CF'!AB21+'QTR CF'!AC21</f>
         <v/>
       </c>
-      <c r="K21" s="5">
+      <c r="J21" s="11">
         <f>'QTR CF'!AD21+'QTR CF'!AE21+'QTR CF'!AF21+'QTR CF'!AG21</f>
         <v/>
       </c>
-      <c r="L21" s="5">
+      <c r="K21" s="11">
         <f>'QTR CF'!AH21+'QTR CF'!AI21+'QTR CF'!AJ21+'QTR CF'!AK21</f>
         <v/>
       </c>
+      <c r="L21" s="5" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -16650,30 +16508,27 @@
       <c r="F22" s="4" t="n">
         <v>-6512</v>
       </c>
-      <c r="G22" s="5">
-        <f>'QTR CF'!N22+'QTR CF'!O22+'QTR CF'!P22+'QTR CF'!Q22</f>
-        <v/>
-      </c>
-      <c r="H22" s="5">
+      <c r="G22" s="11">
         <f>'QTR CF'!R22+'QTR CF'!S22+'QTR CF'!T22+'QTR CF'!U22</f>
         <v/>
       </c>
-      <c r="I22" s="5">
+      <c r="H22" s="11">
         <f>'QTR CF'!V22+'QTR CF'!W22+'QTR CF'!X22+'QTR CF'!Y22</f>
         <v/>
       </c>
-      <c r="J22" s="5">
+      <c r="I22" s="11">
         <f>'QTR CF'!Z22+'QTR CF'!AA22+'QTR CF'!AB22+'QTR CF'!AC22</f>
         <v/>
       </c>
-      <c r="K22" s="5">
+      <c r="J22" s="11">
         <f>'QTR CF'!AD22+'QTR CF'!AE22+'QTR CF'!AF22+'QTR CF'!AG22</f>
         <v/>
       </c>
-      <c r="L22" s="5">
+      <c r="K22" s="11">
         <f>'QTR CF'!AH22+'QTR CF'!AI22+'QTR CF'!AJ22+'QTR CF'!AK22</f>
         <v/>
       </c>
+      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -16696,30 +16551,27 @@
       <c r="F23" s="4" t="n">
         <v>-1138</v>
       </c>
-      <c r="G23" s="5">
-        <f>'QTR CF'!N23+'QTR CF'!O23+'QTR CF'!P23+'QTR CF'!Q23</f>
-        <v/>
-      </c>
-      <c r="H23" s="5">
+      <c r="G23" s="11">
         <f>'QTR CF'!R23+'QTR CF'!S23+'QTR CF'!T23+'QTR CF'!U23</f>
         <v/>
       </c>
-      <c r="I23" s="5">
+      <c r="H23" s="11">
         <f>'QTR CF'!V23+'QTR CF'!W23+'QTR CF'!X23+'QTR CF'!Y23</f>
         <v/>
       </c>
-      <c r="J23" s="5">
+      <c r="I23" s="11">
         <f>'QTR CF'!Z23+'QTR CF'!AA23+'QTR CF'!AB23+'QTR CF'!AC23</f>
         <v/>
       </c>
-      <c r="K23" s="5">
+      <c r="J23" s="11">
         <f>'QTR CF'!AD23+'QTR CF'!AE23+'QTR CF'!AF23+'QTR CF'!AG23</f>
         <v/>
       </c>
-      <c r="L23" s="5">
+      <c r="K23" s="11">
         <f>'QTR CF'!AH23+'QTR CF'!AI23+'QTR CF'!AJ23+'QTR CF'!AK23</f>
         <v/>
       </c>
+      <c r="L23" s="5" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -16742,30 +16594,27 @@
       <c r="F24" s="4" t="n">
         <v>2237</v>
       </c>
-      <c r="G24" s="5">
-        <f>'QTR CF'!N24+'QTR CF'!O24+'QTR CF'!P24+'QTR CF'!Q24</f>
-        <v/>
-      </c>
-      <c r="H24" s="5">
+      <c r="G24" s="11">
         <f>'QTR CF'!R24+'QTR CF'!S24+'QTR CF'!T24+'QTR CF'!U24</f>
         <v/>
       </c>
-      <c r="I24" s="5">
+      <c r="H24" s="11">
         <f>'QTR CF'!V24+'QTR CF'!W24+'QTR CF'!X24+'QTR CF'!Y24</f>
         <v/>
       </c>
-      <c r="J24" s="5">
+      <c r="I24" s="11">
         <f>'QTR CF'!Z24+'QTR CF'!AA24+'QTR CF'!AB24+'QTR CF'!AC24</f>
         <v/>
       </c>
-      <c r="K24" s="5">
+      <c r="J24" s="11">
         <f>'QTR CF'!AD24+'QTR CF'!AE24+'QTR CF'!AF24+'QTR CF'!AG24</f>
         <v/>
       </c>
-      <c r="L24" s="5">
+      <c r="K24" s="11">
         <f>'QTR CF'!AH24+'QTR CF'!AI24+'QTR CF'!AJ24+'QTR CF'!AK24</f>
         <v/>
       </c>
+      <c r="L24" s="5" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -16788,30 +16637,27 @@
       <c r="F25" s="4" t="n">
         <v>-1977</v>
       </c>
-      <c r="G25" s="5">
-        <f>'QTR CF'!N25+'QTR CF'!O25+'QTR CF'!P25+'QTR CF'!Q25</f>
-        <v/>
-      </c>
-      <c r="H25" s="5">
+      <c r="G25" s="11">
         <f>'QTR CF'!R25+'QTR CF'!S25+'QTR CF'!T25+'QTR CF'!U25</f>
         <v/>
       </c>
-      <c r="I25" s="5">
+      <c r="H25" s="11">
         <f>'QTR CF'!V25+'QTR CF'!W25+'QTR CF'!X25+'QTR CF'!Y25</f>
         <v/>
       </c>
-      <c r="J25" s="5">
+      <c r="I25" s="11">
         <f>'QTR CF'!Z25+'QTR CF'!AA25+'QTR CF'!AB25+'QTR CF'!AC25</f>
         <v/>
       </c>
-      <c r="K25" s="5">
+      <c r="J25" s="11">
         <f>'QTR CF'!AD25+'QTR CF'!AE25+'QTR CF'!AF25+'QTR CF'!AG25</f>
         <v/>
       </c>
-      <c r="L25" s="5">
+      <c r="K25" s="11">
         <f>'QTR CF'!AH25+'QTR CF'!AI25+'QTR CF'!AJ25+'QTR CF'!AK25</f>
         <v/>
       </c>
+      <c r="L25" s="5" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -16834,30 +16680,27 @@
       <c r="F26" s="4" t="n">
         <v>-6500</v>
       </c>
-      <c r="G26" s="5">
-        <f>'QTR CF'!N26+'QTR CF'!O26+'QTR CF'!P26+'QTR CF'!Q26</f>
-        <v/>
-      </c>
-      <c r="H26" s="5">
+      <c r="G26" s="11">
         <f>'QTR CF'!R26+'QTR CF'!S26+'QTR CF'!T26+'QTR CF'!U26</f>
         <v/>
       </c>
-      <c r="I26" s="5">
+      <c r="H26" s="11">
         <f>'QTR CF'!V26+'QTR CF'!W26+'QTR CF'!X26+'QTR CF'!Y26</f>
         <v/>
       </c>
-      <c r="J26" s="5">
+      <c r="I26" s="11">
         <f>'QTR CF'!Z26+'QTR CF'!AA26+'QTR CF'!AB26+'QTR CF'!AC26</f>
         <v/>
       </c>
-      <c r="K26" s="5">
+      <c r="J26" s="11">
         <f>'QTR CF'!AD26+'QTR CF'!AE26+'QTR CF'!AF26+'QTR CF'!AG26</f>
         <v/>
       </c>
-      <c r="L26" s="5">
+      <c r="K26" s="11">
         <f>'QTR CF'!AH26+'QTR CF'!AI26+'QTR CF'!AJ26+'QTR CF'!AK26</f>
         <v/>
       </c>
+      <c r="L26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -16880,30 +16723,27 @@
       <c r="F27" s="4" t="n">
         <v>1707</v>
       </c>
-      <c r="G27" s="5">
-        <f>'QTR CF'!N27+'QTR CF'!O27+'QTR CF'!P27+'QTR CF'!Q27</f>
-        <v/>
-      </c>
-      <c r="H27" s="5">
+      <c r="G27" s="11">
         <f>'QTR CF'!R27+'QTR CF'!S27+'QTR CF'!T27+'QTR CF'!U27</f>
         <v/>
       </c>
-      <c r="I27" s="5">
+      <c r="H27" s="11">
         <f>'QTR CF'!V27+'QTR CF'!W27+'QTR CF'!X27+'QTR CF'!Y27</f>
         <v/>
       </c>
-      <c r="J27" s="5">
+      <c r="I27" s="11">
         <f>'QTR CF'!Z27+'QTR CF'!AA27+'QTR CF'!AB27+'QTR CF'!AC27</f>
         <v/>
       </c>
-      <c r="K27" s="5">
+      <c r="J27" s="11">
         <f>'QTR CF'!AD27+'QTR CF'!AE27+'QTR CF'!AF27+'QTR CF'!AG27</f>
         <v/>
       </c>
-      <c r="L27" s="5">
+      <c r="K27" s="11">
         <f>'QTR CF'!AH27+'QTR CF'!AI27+'QTR CF'!AJ27+'QTR CF'!AK27</f>
         <v/>
       </c>
+      <c r="L27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -16977,30 +16817,27 @@
       <c r="F29" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="G29" s="5">
-        <f>'QTR CF'!N29+'QTR CF'!O29+'QTR CF'!P29+'QTR CF'!Q29</f>
-        <v/>
-      </c>
-      <c r="H29" s="5">
+      <c r="G29" s="11">
         <f>'QTR CF'!R29+'QTR CF'!S29+'QTR CF'!T29+'QTR CF'!U29</f>
         <v/>
       </c>
-      <c r="I29" s="5">
+      <c r="H29" s="11">
         <f>'QTR CF'!V29+'QTR CF'!W29+'QTR CF'!X29+'QTR CF'!Y29</f>
         <v/>
       </c>
-      <c r="J29" s="5">
+      <c r="I29" s="11">
         <f>'QTR CF'!Z29+'QTR CF'!AA29+'QTR CF'!AB29+'QTR CF'!AC29</f>
         <v/>
       </c>
-      <c r="K29" s="5">
+      <c r="J29" s="11">
         <f>'QTR CF'!AD29+'QTR CF'!AE29+'QTR CF'!AF29+'QTR CF'!AG29</f>
         <v/>
       </c>
-      <c r="L29" s="5">
+      <c r="K29" s="11">
         <f>'QTR CF'!AH29+'QTR CF'!AI29+'QTR CF'!AJ29+'QTR CF'!AK29</f>
         <v/>
       </c>
+      <c r="L29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -21864,75 +21701,75 @@
         <f>'YTD P&amp;L'!O4-'YTD P&amp;L'!N4</f>
         <v/>
       </c>
-      <c r="T4" s="12">
+      <c r="T4" s="7">
         <f>T2+T3</f>
         <v/>
       </c>
-      <c r="U4" s="12">
+      <c r="U4" s="7">
         <f>U2+U3</f>
         <v/>
       </c>
-      <c r="V4" s="12">
+      <c r="V4" s="7">
         <f>V2+V3</f>
         <v/>
       </c>
-      <c r="W4" s="12">
+      <c r="W4" s="7">
         <f>W2+W3</f>
         <v/>
       </c>
-      <c r="X4" s="12">
+      <c r="X4" s="7">
         <f>X2+X3</f>
         <v/>
       </c>
-      <c r="Y4" s="12">
+      <c r="Y4" s="7">
         <f>Y2+Y3</f>
         <v/>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="7">
         <f>Z2+Z3</f>
         <v/>
       </c>
-      <c r="AA4" s="12">
+      <c r="AA4" s="7">
         <f>AA2+AA3</f>
         <v/>
       </c>
-      <c r="AB4" s="12">
+      <c r="AB4" s="7">
         <f>AB2+AB3</f>
         <v/>
       </c>
-      <c r="AC4" s="12">
+      <c r="AC4" s="7">
         <f>AC2+AC3</f>
         <v/>
       </c>
-      <c r="AD4" s="12">
+      <c r="AD4" s="7">
         <f>AD2+AD3</f>
         <v/>
       </c>
-      <c r="AE4" s="12">
+      <c r="AE4" s="7">
         <f>AE2+AE3</f>
         <v/>
       </c>
-      <c r="AF4" s="12">
+      <c r="AF4" s="7">
         <f>AF2+AF3</f>
         <v/>
       </c>
-      <c r="AG4" s="12">
+      <c r="AG4" s="7">
         <f>AG2+AG3</f>
         <v/>
       </c>
-      <c r="AH4" s="12">
+      <c r="AH4" s="7">
         <f>AH2+AH3</f>
         <v/>
       </c>
-      <c r="AI4" s="12">
+      <c r="AI4" s="7">
         <f>AI2+AI3</f>
         <v/>
       </c>
-      <c r="AJ4" s="12">
+      <c r="AJ4" s="7">
         <f>AJ2+AJ3</f>
         <v/>
       </c>
-      <c r="AK4" s="12">
+      <c r="AK4" s="7">
         <f>AK2+AK3</f>
         <v/>
       </c>
@@ -22317,75 +22154,75 @@
         <f>'YTD P&amp;L'!O7-'YTD P&amp;L'!N7</f>
         <v/>
       </c>
-      <c r="T7" s="12">
+      <c r="T7" s="7">
         <f>T4+SUM(T5:T6)</f>
         <v/>
       </c>
-      <c r="U7" s="12">
+      <c r="U7" s="7">
         <f>U4+SUM(U5:U6)</f>
         <v/>
       </c>
-      <c r="V7" s="12">
+      <c r="V7" s="7">
         <f>V4+SUM(V5:V6)</f>
         <v/>
       </c>
-      <c r="W7" s="12">
+      <c r="W7" s="7">
         <f>W4+SUM(W5:W6)</f>
         <v/>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="7">
         <f>X4+SUM(X5:X6)</f>
         <v/>
       </c>
-      <c r="Y7" s="12">
+      <c r="Y7" s="7">
         <f>Y4+SUM(Y5:Y6)</f>
         <v/>
       </c>
-      <c r="Z7" s="12">
+      <c r="Z7" s="7">
         <f>Z4+SUM(Z5:Z6)</f>
         <v/>
       </c>
-      <c r="AA7" s="12">
+      <c r="AA7" s="7">
         <f>AA4+SUM(AA5:AA6)</f>
         <v/>
       </c>
-      <c r="AB7" s="12">
+      <c r="AB7" s="7">
         <f>AB4+SUM(AB5:AB6)</f>
         <v/>
       </c>
-      <c r="AC7" s="12">
+      <c r="AC7" s="7">
         <f>AC4+SUM(AC5:AC6)</f>
         <v/>
       </c>
-      <c r="AD7" s="12">
+      <c r="AD7" s="7">
         <f>AD4+SUM(AD5:AD6)</f>
         <v/>
       </c>
-      <c r="AE7" s="12">
+      <c r="AE7" s="7">
         <f>AE4+SUM(AE5:AE6)</f>
         <v/>
       </c>
-      <c r="AF7" s="12">
+      <c r="AF7" s="7">
         <f>AF4+SUM(AF5:AF6)</f>
         <v/>
       </c>
-      <c r="AG7" s="12">
+      <c r="AG7" s="7">
         <f>AG4+SUM(AG5:AG6)</f>
         <v/>
       </c>
-      <c r="AH7" s="12">
+      <c r="AH7" s="7">
         <f>AH4+SUM(AH5:AH6)</f>
         <v/>
       </c>
-      <c r="AI7" s="12">
+      <c r="AI7" s="7">
         <f>AI4+SUM(AI5:AI6)</f>
         <v/>
       </c>
-      <c r="AJ7" s="12">
+      <c r="AJ7" s="7">
         <f>AJ4+SUM(AJ5:AJ6)</f>
         <v/>
       </c>
-      <c r="AK7" s="12">
+      <c r="AK7" s="7">
         <f>AK4+SUM(AK5:AK6)</f>
         <v/>
       </c>
@@ -22770,75 +22607,75 @@
         <f>'YTD P&amp;L'!O10-'YTD P&amp;L'!N10</f>
         <v/>
       </c>
-      <c r="T10" s="12">
+      <c r="T10" s="7">
         <f>T7+SUM(T8:T9)</f>
         <v/>
       </c>
-      <c r="U10" s="12">
+      <c r="U10" s="7">
         <f>U7+SUM(U8:U9)</f>
         <v/>
       </c>
-      <c r="V10" s="12">
+      <c r="V10" s="7">
         <f>V7+SUM(V8:V9)</f>
         <v/>
       </c>
-      <c r="W10" s="12">
+      <c r="W10" s="7">
         <f>W7+SUM(W8:W9)</f>
         <v/>
       </c>
-      <c r="X10" s="12">
+      <c r="X10" s="7">
         <f>X7+SUM(X8:X9)</f>
         <v/>
       </c>
-      <c r="Y10" s="12">
+      <c r="Y10" s="7">
         <f>Y7+SUM(Y8:Y9)</f>
         <v/>
       </c>
-      <c r="Z10" s="12">
+      <c r="Z10" s="7">
         <f>Z7+SUM(Z8:Z9)</f>
         <v/>
       </c>
-      <c r="AA10" s="12">
+      <c r="AA10" s="7">
         <f>AA7+SUM(AA8:AA9)</f>
         <v/>
       </c>
-      <c r="AB10" s="12">
+      <c r="AB10" s="7">
         <f>AB7+SUM(AB8:AB9)</f>
         <v/>
       </c>
-      <c r="AC10" s="12">
+      <c r="AC10" s="7">
         <f>AC7+SUM(AC8:AC9)</f>
         <v/>
       </c>
-      <c r="AD10" s="12">
+      <c r="AD10" s="7">
         <f>AD7+SUM(AD8:AD9)</f>
         <v/>
       </c>
-      <c r="AE10" s="12">
+      <c r="AE10" s="7">
         <f>AE7+SUM(AE8:AE9)</f>
         <v/>
       </c>
-      <c r="AF10" s="12">
+      <c r="AF10" s="7">
         <f>AF7+SUM(AF8:AF9)</f>
         <v/>
       </c>
-      <c r="AG10" s="12">
+      <c r="AG10" s="7">
         <f>AG7+SUM(AG8:AG9)</f>
         <v/>
       </c>
-      <c r="AH10" s="12">
+      <c r="AH10" s="7">
         <f>AH7+SUM(AH8:AH9)</f>
         <v/>
       </c>
-      <c r="AI10" s="12">
+      <c r="AI10" s="7">
         <f>AI7+SUM(AI8:AI9)</f>
         <v/>
       </c>
-      <c r="AJ10" s="12">
+      <c r="AJ10" s="7">
         <f>AJ7+SUM(AJ8:AJ9)</f>
         <v/>
       </c>
-      <c r="AK10" s="12">
+      <c r="AK10" s="7">
         <f>AK7+SUM(AK8:AK9)</f>
         <v/>
       </c>
@@ -23072,75 +22909,75 @@
         <f>'YTD P&amp;L'!O12-'YTD P&amp;L'!N12</f>
         <v/>
       </c>
-      <c r="T12" s="12">
+      <c r="T12" s="7">
         <f>T10+T11</f>
         <v/>
       </c>
-      <c r="U12" s="12">
+      <c r="U12" s="7">
         <f>U10+U11</f>
         <v/>
       </c>
-      <c r="V12" s="12">
+      <c r="V12" s="7">
         <f>V10+V11</f>
         <v/>
       </c>
-      <c r="W12" s="12">
+      <c r="W12" s="7">
         <f>W10+W11</f>
         <v/>
       </c>
-      <c r="X12" s="12">
+      <c r="X12" s="7">
         <f>X10+X11</f>
         <v/>
       </c>
-      <c r="Y12" s="12">
+      <c r="Y12" s="7">
         <f>Y10+Y11</f>
         <v/>
       </c>
-      <c r="Z12" s="12">
+      <c r="Z12" s="7">
         <f>Z10+Z11</f>
         <v/>
       </c>
-      <c r="AA12" s="12">
+      <c r="AA12" s="7">
         <f>AA10+AA11</f>
         <v/>
       </c>
-      <c r="AB12" s="12">
+      <c r="AB12" s="7">
         <f>AB10+AB11</f>
         <v/>
       </c>
-      <c r="AC12" s="12">
+      <c r="AC12" s="7">
         <f>AC10+AC11</f>
         <v/>
       </c>
-      <c r="AD12" s="12">
+      <c r="AD12" s="7">
         <f>AD10+AD11</f>
         <v/>
       </c>
-      <c r="AE12" s="12">
+      <c r="AE12" s="7">
         <f>AE10+AE11</f>
         <v/>
       </c>
-      <c r="AF12" s="12">
+      <c r="AF12" s="7">
         <f>AF10+AF11</f>
         <v/>
       </c>
-      <c r="AG12" s="12">
+      <c r="AG12" s="7">
         <f>AG10+AG11</f>
         <v/>
       </c>
-      <c r="AH12" s="12">
+      <c r="AH12" s="7">
         <f>AH10+AH11</f>
         <v/>
       </c>
-      <c r="AI12" s="12">
+      <c r="AI12" s="7">
         <f>AI10+AI11</f>
         <v/>
       </c>
-      <c r="AJ12" s="12">
+      <c r="AJ12" s="7">
         <f>AJ10+AJ11</f>
         <v/>
       </c>
-      <c r="AK12" s="12">
+      <c r="AK12" s="7">
         <f>AK10+AK11</f>
         <v/>
       </c>
@@ -24308,75 +24145,75 @@
         <f>'YTD BS'!P6</f>
         <v/>
       </c>
-      <c r="Q6" s="12">
+      <c r="Q6" s="7">
         <f>SUM(Q2:Q5)</f>
         <v/>
       </c>
-      <c r="R6" s="12">
+      <c r="R6" s="7">
         <f>SUM(R2:R5)</f>
         <v/>
       </c>
-      <c r="S6" s="12">
+      <c r="S6" s="7">
         <f>SUM(S2:S5)</f>
         <v/>
       </c>
-      <c r="T6" s="12">
+      <c r="T6" s="7">
         <f>SUM(T2:T5)</f>
         <v/>
       </c>
-      <c r="U6" s="12">
+      <c r="U6" s="7">
         <f>SUM(U2:U5)</f>
         <v/>
       </c>
-      <c r="V6" s="12">
+      <c r="V6" s="7">
         <f>SUM(V2:V5)</f>
         <v/>
       </c>
-      <c r="W6" s="12">
+      <c r="W6" s="7">
         <f>SUM(W2:W5)</f>
         <v/>
       </c>
-      <c r="X6" s="12">
+      <c r="X6" s="7">
         <f>SUM(X2:X5)</f>
         <v/>
       </c>
-      <c r="Y6" s="12">
+      <c r="Y6" s="7">
         <f>SUM(Y2:Y5)</f>
         <v/>
       </c>
-      <c r="Z6" s="12">
+      <c r="Z6" s="7">
         <f>SUM(Z2:Z5)</f>
         <v/>
       </c>
-      <c r="AA6" s="12">
+      <c r="AA6" s="7">
         <f>SUM(AA2:AA5)</f>
         <v/>
       </c>
-      <c r="AB6" s="12">
+      <c r="AB6" s="7">
         <f>SUM(AB2:AB5)</f>
         <v/>
       </c>
-      <c r="AC6" s="12">
+      <c r="AC6" s="7">
         <f>SUM(AC2:AC5)</f>
         <v/>
       </c>
-      <c r="AD6" s="12">
+      <c r="AD6" s="7">
         <f>SUM(AD2:AD5)</f>
         <v/>
       </c>
-      <c r="AE6" s="12">
+      <c r="AE6" s="7">
         <f>SUM(AE2:AE5)</f>
         <v/>
       </c>
-      <c r="AF6" s="12">
+      <c r="AF6" s="7">
         <f>SUM(AF2:AF5)</f>
         <v/>
       </c>
-      <c r="AG6" s="12">
+      <c r="AG6" s="7">
         <f>SUM(AG2:AG5)</f>
         <v/>
       </c>
-      <c r="AH6" s="12">
+      <c r="AH6" s="7">
         <f>SUM(AH2:AH5)</f>
         <v/>
       </c>
@@ -25003,75 +24840,75 @@
         <f>'YTD BS'!P11</f>
         <v/>
       </c>
-      <c r="Q11" s="12">
+      <c r="Q11" s="7">
         <f>Q6+SUM(Q7:Q10)</f>
         <v/>
       </c>
-      <c r="R11" s="12">
+      <c r="R11" s="7">
         <f>R6+SUM(R7:R10)</f>
         <v/>
       </c>
-      <c r="S11" s="12">
+      <c r="S11" s="7">
         <f>S6+SUM(S7:S10)</f>
         <v/>
       </c>
-      <c r="T11" s="12">
+      <c r="T11" s="7">
         <f>T6+SUM(T7:T10)</f>
         <v/>
       </c>
-      <c r="U11" s="12">
+      <c r="U11" s="7">
         <f>U6+SUM(U7:U10)</f>
         <v/>
       </c>
-      <c r="V11" s="12">
+      <c r="V11" s="7">
         <f>V6+SUM(V7:V10)</f>
         <v/>
       </c>
-      <c r="W11" s="12">
+      <c r="W11" s="7">
         <f>W6+SUM(W7:W10)</f>
         <v/>
       </c>
-      <c r="X11" s="12">
+      <c r="X11" s="7">
         <f>X6+SUM(X7:X10)</f>
         <v/>
       </c>
-      <c r="Y11" s="12">
+      <c r="Y11" s="7">
         <f>Y6+SUM(Y7:Y10)</f>
         <v/>
       </c>
-      <c r="Z11" s="12">
+      <c r="Z11" s="7">
         <f>Z6+SUM(Z7:Z10)</f>
         <v/>
       </c>
-      <c r="AA11" s="12">
+      <c r="AA11" s="7">
         <f>AA6+SUM(AA7:AA10)</f>
         <v/>
       </c>
-      <c r="AB11" s="12">
+      <c r="AB11" s="7">
         <f>AB6+SUM(AB7:AB10)</f>
         <v/>
       </c>
-      <c r="AC11" s="12">
+      <c r="AC11" s="7">
         <f>AC6+SUM(AC7:AC10)</f>
         <v/>
       </c>
-      <c r="AD11" s="12">
+      <c r="AD11" s="7">
         <f>AD6+SUM(AD7:AD10)</f>
         <v/>
       </c>
-      <c r="AE11" s="12">
+      <c r="AE11" s="7">
         <f>AE6+SUM(AE7:AE10)</f>
         <v/>
       </c>
-      <c r="AF11" s="12">
+      <c r="AF11" s="7">
         <f>AF6+SUM(AF7:AF10)</f>
         <v/>
       </c>
-      <c r="AG11" s="12">
+      <c r="AG11" s="7">
         <f>AG6+SUM(AG7:AG10)</f>
         <v/>
       </c>
-      <c r="AH11" s="12">
+      <c r="AH11" s="7">
         <f>AH6+SUM(AH7:AH10)</f>
         <v/>
       </c>
@@ -25559,75 +25396,75 @@
         <f>'YTD BS'!P15</f>
         <v/>
       </c>
-      <c r="Q15" s="12">
+      <c r="Q15" s="7">
         <f>SUM(Q12:Q14)</f>
         <v/>
       </c>
-      <c r="R15" s="12">
+      <c r="R15" s="7">
         <f>SUM(R12:R14)</f>
         <v/>
       </c>
-      <c r="S15" s="12">
+      <c r="S15" s="7">
         <f>SUM(S12:S14)</f>
         <v/>
       </c>
-      <c r="T15" s="12">
+      <c r="T15" s="7">
         <f>SUM(T12:T14)</f>
         <v/>
       </c>
-      <c r="U15" s="12">
+      <c r="U15" s="7">
         <f>SUM(U12:U14)</f>
         <v/>
       </c>
-      <c r="V15" s="12">
+      <c r="V15" s="7">
         <f>SUM(V12:V14)</f>
         <v/>
       </c>
-      <c r="W15" s="12">
+      <c r="W15" s="7">
         <f>SUM(W12:W14)</f>
         <v/>
       </c>
-      <c r="X15" s="12">
+      <c r="X15" s="7">
         <f>SUM(X12:X14)</f>
         <v/>
       </c>
-      <c r="Y15" s="12">
+      <c r="Y15" s="7">
         <f>SUM(Y12:Y14)</f>
         <v/>
       </c>
-      <c r="Z15" s="12">
+      <c r="Z15" s="7">
         <f>SUM(Z12:Z14)</f>
         <v/>
       </c>
-      <c r="AA15" s="12">
+      <c r="AA15" s="7">
         <f>SUM(AA12:AA14)</f>
         <v/>
       </c>
-      <c r="AB15" s="12">
+      <c r="AB15" s="7">
         <f>SUM(AB12:AB14)</f>
         <v/>
       </c>
-      <c r="AC15" s="12">
+      <c r="AC15" s="7">
         <f>SUM(AC12:AC14)</f>
         <v/>
       </c>
-      <c r="AD15" s="12">
+      <c r="AD15" s="7">
         <f>SUM(AD12:AD14)</f>
         <v/>
       </c>
-      <c r="AE15" s="12">
+      <c r="AE15" s="7">
         <f>SUM(AE12:AE14)</f>
         <v/>
       </c>
-      <c r="AF15" s="12">
+      <c r="AF15" s="7">
         <f>SUM(AF12:AF14)</f>
         <v/>
       </c>
-      <c r="AG15" s="12">
+      <c r="AG15" s="7">
         <f>SUM(AG12:AG14)</f>
         <v/>
       </c>
-      <c r="AH15" s="12">
+      <c r="AH15" s="7">
         <f>SUM(AH12:AH14)</f>
         <v/>
       </c>
@@ -26115,75 +25952,75 @@
         <f>'YTD BS'!P19</f>
         <v/>
       </c>
-      <c r="Q19" s="12">
+      <c r="Q19" s="7">
         <f>Q15+SUM(Q16:Q18)</f>
         <v/>
       </c>
-      <c r="R19" s="12">
+      <c r="R19" s="7">
         <f>R15+SUM(R16:R18)</f>
         <v/>
       </c>
-      <c r="S19" s="12">
+      <c r="S19" s="7">
         <f>S15+SUM(S16:S18)</f>
         <v/>
       </c>
-      <c r="T19" s="12">
+      <c r="T19" s="7">
         <f>T15+SUM(T16:T18)</f>
         <v/>
       </c>
-      <c r="U19" s="12">
+      <c r="U19" s="7">
         <f>U15+SUM(U16:U18)</f>
         <v/>
       </c>
-      <c r="V19" s="12">
+      <c r="V19" s="7">
         <f>V15+SUM(V16:V18)</f>
         <v/>
       </c>
-      <c r="W19" s="12">
+      <c r="W19" s="7">
         <f>W15+SUM(W16:W18)</f>
         <v/>
       </c>
-      <c r="X19" s="12">
+      <c r="X19" s="7">
         <f>X15+SUM(X16:X18)</f>
         <v/>
       </c>
-      <c r="Y19" s="12">
+      <c r="Y19" s="7">
         <f>Y15+SUM(Y16:Y18)</f>
         <v/>
       </c>
-      <c r="Z19" s="12">
+      <c r="Z19" s="7">
         <f>Z15+SUM(Z16:Z18)</f>
         <v/>
       </c>
-      <c r="AA19" s="12">
+      <c r="AA19" s="7">
         <f>AA15+SUM(AA16:AA18)</f>
         <v/>
       </c>
-      <c r="AB19" s="12">
+      <c r="AB19" s="7">
         <f>AB15+SUM(AB16:AB18)</f>
         <v/>
       </c>
-      <c r="AC19" s="12">
+      <c r="AC19" s="7">
         <f>AC15+SUM(AC16:AC18)</f>
         <v/>
       </c>
-      <c r="AD19" s="12">
+      <c r="AD19" s="7">
         <f>AD15+SUM(AD16:AD18)</f>
         <v/>
       </c>
-      <c r="AE19" s="12">
+      <c r="AE19" s="7">
         <f>AE15+SUM(AE16:AE18)</f>
         <v/>
       </c>
-      <c r="AF19" s="12">
+      <c r="AF19" s="7">
         <f>AF15+SUM(AF16:AF18)</f>
         <v/>
       </c>
-      <c r="AG19" s="12">
+      <c r="AG19" s="7">
         <f>AG15+SUM(AG16:AG18)</f>
         <v/>
       </c>
-      <c r="AH19" s="12">
+      <c r="AH19" s="7">
         <f>AH15+SUM(AH16:AH18)</f>
         <v/>
       </c>
@@ -27366,75 +27203,75 @@
         <f>'YTD BS'!P28</f>
         <v/>
       </c>
-      <c r="Q28" s="12">
+      <c r="Q28" s="7">
         <f>SUM(Q20:Q27)</f>
         <v/>
       </c>
-      <c r="R28" s="12">
+      <c r="R28" s="7">
         <f>SUM(R20:R27)</f>
         <v/>
       </c>
-      <c r="S28" s="12">
+      <c r="S28" s="7">
         <f>SUM(S20:S27)</f>
         <v/>
       </c>
-      <c r="T28" s="12">
+      <c r="T28" s="7">
         <f>SUM(T20:T27)</f>
         <v/>
       </c>
-      <c r="U28" s="12">
+      <c r="U28" s="7">
         <f>SUM(U20:U27)</f>
         <v/>
       </c>
-      <c r="V28" s="12">
+      <c r="V28" s="7">
         <f>SUM(V20:V27)</f>
         <v/>
       </c>
-      <c r="W28" s="12">
+      <c r="W28" s="7">
         <f>SUM(W20:W27)</f>
         <v/>
       </c>
-      <c r="X28" s="12">
+      <c r="X28" s="7">
         <f>SUM(X20:X27)</f>
         <v/>
       </c>
-      <c r="Y28" s="12">
+      <c r="Y28" s="7">
         <f>SUM(Y20:Y27)</f>
         <v/>
       </c>
-      <c r="Z28" s="12">
+      <c r="Z28" s="7">
         <f>SUM(Z20:Z27)</f>
         <v/>
       </c>
-      <c r="AA28" s="12">
+      <c r="AA28" s="7">
         <f>SUM(AA20:AA27)</f>
         <v/>
       </c>
-      <c r="AB28" s="12">
+      <c r="AB28" s="7">
         <f>SUM(AB20:AB27)</f>
         <v/>
       </c>
-      <c r="AC28" s="12">
+      <c r="AC28" s="7">
         <f>SUM(AC20:AC27)</f>
         <v/>
       </c>
-      <c r="AD28" s="12">
+      <c r="AD28" s="7">
         <f>SUM(AD20:AD27)</f>
         <v/>
       </c>
-      <c r="AE28" s="12">
+      <c r="AE28" s="7">
         <f>SUM(AE20:AE27)</f>
         <v/>
       </c>
-      <c r="AF28" s="12">
+      <c r="AF28" s="7">
         <f>SUM(AF20:AF27)</f>
         <v/>
       </c>
-      <c r="AG28" s="12">
+      <c r="AG28" s="7">
         <f>SUM(AG20:AG27)</f>
         <v/>
       </c>
-      <c r="AH28" s="12">
+      <c r="AH28" s="7">
         <f>SUM(AH20:AH27)</f>
         <v/>
       </c>
@@ -27505,75 +27342,75 @@
         <f>'YTD BS'!P29</f>
         <v/>
       </c>
-      <c r="Q29" s="12">
+      <c r="Q29" s="7">
         <f>Q19+Q28</f>
         <v/>
       </c>
-      <c r="R29" s="12">
+      <c r="R29" s="7">
         <f>R19+R28</f>
         <v/>
       </c>
-      <c r="S29" s="12">
+      <c r="S29" s="7">
         <f>S19+S28</f>
         <v/>
       </c>
-      <c r="T29" s="12">
+      <c r="T29" s="7">
         <f>T19+T28</f>
         <v/>
       </c>
-      <c r="U29" s="12">
+      <c r="U29" s="7">
         <f>U19+U28</f>
         <v/>
       </c>
-      <c r="V29" s="12">
+      <c r="V29" s="7">
         <f>V19+V28</f>
         <v/>
       </c>
-      <c r="W29" s="12">
+      <c r="W29" s="7">
         <f>W19+W28</f>
         <v/>
       </c>
-      <c r="X29" s="12">
+      <c r="X29" s="7">
         <f>X19+X28</f>
         <v/>
       </c>
-      <c r="Y29" s="12">
+      <c r="Y29" s="7">
         <f>Y19+Y28</f>
         <v/>
       </c>
-      <c r="Z29" s="12">
+      <c r="Z29" s="7">
         <f>Z19+Z28</f>
         <v/>
       </c>
-      <c r="AA29" s="12">
+      <c r="AA29" s="7">
         <f>AA19+AA28</f>
         <v/>
       </c>
-      <c r="AB29" s="12">
+      <c r="AB29" s="7">
         <f>AB19+AB28</f>
         <v/>
       </c>
-      <c r="AC29" s="12">
+      <c r="AC29" s="7">
         <f>AC19+AC28</f>
         <v/>
       </c>
-      <c r="AD29" s="12">
+      <c r="AD29" s="7">
         <f>AD19+AD28</f>
         <v/>
       </c>
-      <c r="AE29" s="12">
+      <c r="AE29" s="7">
         <f>AE19+AE28</f>
         <v/>
       </c>
-      <c r="AF29" s="12">
+      <c r="AF29" s="7">
         <f>AF19+AF28</f>
         <v/>
       </c>
-      <c r="AG29" s="12">
+      <c r="AG29" s="7">
         <f>AG19+AG28</f>
         <v/>
       </c>
-      <c r="AH29" s="12">
+      <c r="AH29" s="7">
         <f>AH19+AH28</f>
         <v/>
       </c>
